--- a/Frontera/Empleados.xlsx
+++ b/Frontera/Empleados.xlsx
@@ -1,26 +1,44 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\TarjetasQR\Frontera\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47B893CA-9266-4ADC-B56D-377C4B4BBBFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11715"/>
   </bookViews>
   <sheets>
     <sheet name="Empleados" sheetId="1" r:id="rId1"/>
+    <sheet name="Hoja1" sheetId="2" r:id="rId2"/>
+    <sheet name="Hoja2" sheetId="3" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Hoja1!$A$1:$D$107</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Hoja2!$A$1:$F$67</definedName>
+  </definedNames>
   <calcPr calcId="152511"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="857" uniqueCount="156">
   <si>
     <t>Id</t>
   </si>
@@ -55,6 +73,9 @@
     <t>Telefono_internacional</t>
   </si>
   <si>
+    <t>MARIA DEL PILAR GOMEZ MORA</t>
+  </si>
+  <si>
     <t>Company Man</t>
   </si>
   <si>
@@ -188,6 +209,216 @@
   </si>
   <si>
     <t>gilbertorubiano@yahoo.com</t>
+  </si>
+  <si>
+    <t>PERSONAL</t>
+  </si>
+  <si>
+    <t>SERVICIO CxC</t>
+  </si>
+  <si>
+    <t>ING LIDER/EQUIPO</t>
+  </si>
+  <si>
+    <t>MES</t>
+  </si>
+  <si>
+    <t>MARIA MONICA SIERRA CESPEDES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PETROMINERALES No. 5500006789 D1                                                </t>
+  </si>
+  <si>
+    <t>OLGA AMPUDIA - IND-26</t>
+  </si>
+  <si>
+    <t>ENERO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PETROMINERALES No. 5500006789 D2                                                </t>
+  </si>
+  <si>
+    <t>OLGA AMPUDIA_IND-26</t>
+  </si>
+  <si>
+    <t>FEBRERO</t>
+  </si>
+  <si>
+    <t>DANNY KARINA ORTIZ ORTIZ</t>
+  </si>
+  <si>
+    <t>OLGA AMPUDIA_CT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PETROMINERALES No. 5500006789 D3                                                </t>
+  </si>
+  <si>
+    <t xml:space="preserve">METAPETROLEUM  No. 5500006806  D1                                                </t>
+  </si>
+  <si>
+    <t>CARLOS MORALES-IND-47</t>
+  </si>
+  <si>
+    <t xml:space="preserve">METAPETROLEUM  No. 5500006806  D2                                                </t>
+  </si>
+  <si>
+    <t>MARZO</t>
+  </si>
+  <si>
+    <t>ABRIL</t>
+  </si>
+  <si>
+    <t>MAYO</t>
+  </si>
+  <si>
+    <t>MIGUEL OCTAVIO FIERRO CASTRO</t>
+  </si>
+  <si>
+    <t>ARTURO LARSEN - IND-34</t>
+  </si>
+  <si>
+    <t>KAREN LORENA SALCEDO VALDERRAMA</t>
+  </si>
+  <si>
+    <t>DANIEL CELMA- IND-34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PETROMINERALES No. 5500006789 D1 DIA                                 </t>
+  </si>
+  <si>
+    <t>YENNY TALERO_CT</t>
+  </si>
+  <si>
+    <t>ALVARO JAVIER QUIMBAYA MONTEALEGRE</t>
+  </si>
+  <si>
+    <t>YENNY TALERO_RSU SETIP</t>
+  </si>
+  <si>
+    <t>OSCAR FERNANDO BELLO RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>CARLOS MORALES_RSU SETIP</t>
+  </si>
+  <si>
+    <t>JUNIO</t>
+  </si>
+  <si>
+    <t>JULIO</t>
+  </si>
+  <si>
+    <t>ARTURO LARSEN_CT</t>
+  </si>
+  <si>
+    <t>MARIA PAULA TELLEZ_PTW118</t>
+  </si>
+  <si>
+    <t>PAOLA ADRIANA GIL CHIPATECUA</t>
+  </si>
+  <si>
+    <t>YEIMY LORENA QUINTERO LIZCANO</t>
+  </si>
+  <si>
+    <t>AGOSTO</t>
+  </si>
+  <si>
+    <t>SEPTIEMBRE</t>
+  </si>
+  <si>
+    <t>MARIA PAULA TELLEZ_PTW-118</t>
+  </si>
+  <si>
+    <t>DICIEMBRE</t>
+  </si>
+  <si>
+    <t>JEFFERSON JULIAN SANABRIA AMAYA</t>
+  </si>
+  <si>
+    <t>ANGELA MARTINEZ_IND-61</t>
+  </si>
+  <si>
+    <t>RICARDO ANDRES VARGAS CORREDOR</t>
+  </si>
+  <si>
+    <t>ANGELA MARTINEZ_IND-50</t>
+  </si>
+  <si>
+    <t>JOSE ANIBAL AMADOR RAMOS</t>
+  </si>
+  <si>
+    <t>MARIA PAULA TELLEZ_PTW153</t>
+  </si>
+  <si>
+    <t>ARTURO LARSEN</t>
+  </si>
+  <si>
+    <t>OLGA AMPUDIA_IND-43</t>
+  </si>
+  <si>
+    <t>OLGA AMPUDIA</t>
+  </si>
+  <si>
+    <t>DANIEL CELMA_IND-43</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PETROMINERALES No. 5500006789 D3 DIA                                 </t>
+  </si>
+  <si>
+    <t>OCTUBRE</t>
+  </si>
+  <si>
+    <t>NOVIEMBRE</t>
+  </si>
+  <si>
+    <t>DANIEL CELMA</t>
+  </si>
+  <si>
+    <t>FEB-JUL</t>
+  </si>
+  <si>
+    <t>OCT-DIC</t>
+  </si>
+  <si>
+    <t>FEB-MAY</t>
+  </si>
+  <si>
+    <t>FEB-JUN</t>
+  </si>
+  <si>
+    <t>FEB-MAR</t>
+  </si>
+  <si>
+    <t>FEB-ABR</t>
+  </si>
+  <si>
+    <t>FEB-AGO</t>
+  </si>
+  <si>
+    <t>JUN-SEP</t>
+  </si>
+  <si>
+    <t>MAR-MAY</t>
+  </si>
+  <si>
+    <t>AGO-SEP</t>
+  </si>
+  <si>
+    <t>MAR-MAR</t>
+  </si>
+  <si>
+    <t>ENE-ABR</t>
+  </si>
+  <si>
+    <t>OCT-NOV</t>
+  </si>
+  <si>
+    <t>ENE-JUN</t>
+  </si>
+  <si>
+    <t>ENE-SEP</t>
+  </si>
+  <si>
+    <t>DIC-DIC</t>
   </si>
   <si>
     <t>Numero_
@@ -239,17 +470,50 @@
     <t>https://drive.google.com/file/d/1nUYN37ScJMbkhzxxRFi8zqwuSy3lQcoR/view?usp=sharing</t>
   </si>
   <si>
+    <t>FECHA INICIO</t>
+  </si>
+  <si>
+    <t>FECHA FINAL</t>
+  </si>
+  <si>
+    <t>ABRIL-MAYO</t>
+  </si>
+  <si>
+    <t>MAY-JUNIO</t>
+  </si>
+  <si>
+    <t>ENE-FEB</t>
+  </si>
+  <si>
+    <t>PERIODO</t>
+  </si>
+  <si>
+    <t>5//6</t>
+  </si>
+  <si>
+    <t>8//*9</t>
+  </si>
+  <si>
+    <t>1//2</t>
+  </si>
+  <si>
+    <t>4//5</t>
+  </si>
+  <si>
+    <t>2//3</t>
+  </si>
+  <si>
     <t>https://drive.google.com/file/d/1ruxKILQaJ8aK07h7fOK6lIkGd-JVgtwp/view?usp=sharing</t>
   </si>
   <si>
-    <t>(1) 713 623 1113</t>
+    <t>(1)7136231113</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -392,8 +656,25 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Arial Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial Narrow"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="33">
+  <fills count="38">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -573,8 +854,38 @@
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00FF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00FF00"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="10">
+  <borders count="40">
     <border>
       <left/>
       <right/>
@@ -689,6 +1000,422 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.14999847407452621"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.14999847407452621"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.14999847407452621"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.14999847407452621"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.14999847407452621"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.14999847407452621"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.14999847407452621"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.14999847407452621"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color theme="0" tint="-0.14999847407452621"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.14999847407452621"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.14999847407452621"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.14999847407452621"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.14999847407452621"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0" tint="-0.14999847407452621"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.14999847407452621"/>
+      </right>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.14999847407452621"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -735,7 +1462,7 @@
     <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -746,11 +1473,208 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="42" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="33" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="20" fillId="33" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="35" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="35" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="35" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="35" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="35" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="35" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="35" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="36" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="37" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="19" fillId="37" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="37" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="20" fillId="37" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="37" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="20" fillId="37" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="20" fillId="37" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="21" fillId="37" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="19" fillId="37" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="37" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="20" fillId="37" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="37" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="19" fillId="37" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="20" fillId="37" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="37" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="37" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="37" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="37" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="37" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="37" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="19" fillId="37" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="20" fillId="37" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="37" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="20" fillId="37" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="37" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="19" fillId="37" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="20" fillId="37" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="20" fillId="37" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="37" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="20" fillId="37" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="37" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="20" fillId="37" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="19" fillId="37" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="21" fillId="37" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="37" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="20" fillId="37" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="19" fillId="37" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="37" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="37" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="20" fillId="37" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="20" fillId="37" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="43">
@@ -772,7 +1696,7 @@
     <cellStyle name="60% - Énfasis4" xfId="33" builtinId="44" customBuiltin="1"/>
     <cellStyle name="60% - Énfasis5" xfId="37" builtinId="48" customBuiltin="1"/>
     <cellStyle name="60% - Énfasis6" xfId="41" builtinId="52" customBuiltin="1"/>
-    <cellStyle name="Bueno" xfId="6" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="Buena" xfId="6" builtinId="26" customBuiltin="1"/>
     <cellStyle name="Cálculo" xfId="11" builtinId="22" customBuiltin="1"/>
     <cellStyle name="Celda de comprobación" xfId="13" builtinId="23" customBuiltin="1"/>
     <cellStyle name="Celda vinculada" xfId="12" builtinId="24" customBuiltin="1"/>
@@ -803,10 +1727,10 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -830,13 +1754,13 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="left" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -852,23 +1776,23 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabla1" displayName="Tabla1" ref="A1:K21" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
-  <autoFilter ref="A1:K21" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A5:K21">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabla1" displayName="Tabla1" ref="A1:K21" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
+  <autoFilter ref="A1:K21"/>
+  <sortState ref="A5:K21">
     <sortCondition ref="B1:B21"/>
   </sortState>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="10"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Nombre completo" dataDxfId="9"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Cargo" dataDxfId="8"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Numero__x000a_telefonico" dataDxfId="7"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Tipo de sangre " dataDxfId="6"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="ARL" dataDxfId="5"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Email" dataDxfId="4"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Compania" dataDxfId="3"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Telefono_empresa" dataDxfId="2"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Telefono_internacional" dataDxfId="1"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="imageUrl" dataDxfId="0"/>
+    <tableColumn id="1" name="Id" dataDxfId="10"/>
+    <tableColumn id="2" name="Nombre completo" dataDxfId="9"/>
+    <tableColumn id="3" name="Cargo" dataDxfId="8"/>
+    <tableColumn id="4" name="Numero__x000a_telefonico" dataDxfId="7"/>
+    <tableColumn id="11" name="Tipo de sangre " dataDxfId="6"/>
+    <tableColumn id="10" name="ARL" dataDxfId="5"/>
+    <tableColumn id="5" name="Email" dataDxfId="4"/>
+    <tableColumn id="6" name="Compania" dataDxfId="3"/>
+    <tableColumn id="7" name="Telefono_empresa" dataDxfId="2"/>
+    <tableColumn id="8" name="Telefono_internacional" dataDxfId="1"/>
+    <tableColumn id="9" name="imageUrl" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1136,795 +2060,3887 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K21"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:K29"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="1" width="16.85546875" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
     <col min="3" max="3" width="23.85546875" customWidth="1"/>
-    <col min="4" max="4" width="14.28515625" customWidth="1"/>
-    <col min="5" max="5" width="8.85546875" customWidth="1"/>
-    <col min="6" max="6" width="9.140625" customWidth="1"/>
+    <col min="4" max="4" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.140625" customWidth="1"/>
+    <col min="6" max="6" width="8.85546875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="26.7109375" customWidth="1"/>
     <col min="8" max="8" width="26.28515625" customWidth="1"/>
-    <col min="9" max="9" width="24.5703125" customWidth="1"/>
-    <col min="10" max="10" width="29" customWidth="1"/>
-    <col min="11" max="11" width="78.140625" customWidth="1"/>
+    <col min="9" max="9" width="16.85546875" customWidth="1"/>
+    <col min="10" max="10" width="21.85546875" customWidth="1"/>
+    <col min="11" max="11" width="82.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="4" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:11" s="2" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C1" s="4" t="s">
+      <c r="B1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="E1" s="5" t="s">
+      <c r="D1" s="71" t="s">
+        <v>127</v>
+      </c>
+      <c r="E1" s="71" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="J1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="K1" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>3</v>
+      <c r="A2" s="2">
+        <v>80095582</v>
       </c>
       <c r="B2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D2" s="1">
         <v>3142157622</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="I2" s="1">
+      <c r="I2" s="72">
         <v>3138174050</v>
       </c>
-      <c r="J2" s="1" t="s">
-        <v>73</v>
+      <c r="J2" s="72" t="s">
+        <v>155</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>69</v>
+        <v>140</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>3</v>
+      <c r="A3" s="2">
+        <v>1079181735</v>
       </c>
       <c r="B3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>61</v>
+        <v>132</v>
       </c>
       <c r="D3" s="1">
         <v>3208449808</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="I3" s="1">
+      <c r="I3" s="72">
         <v>3138174050</v>
       </c>
-      <c r="J3" s="1" t="s">
-        <v>73</v>
+      <c r="J3" s="72" t="s">
+        <v>155</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>68</v>
+        <v>139</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
+      <c r="A4" s="2">
+        <v>1121924878</v>
       </c>
       <c r="B4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>61</v>
+        <v>132</v>
       </c>
       <c r="D4" s="1">
         <v>3124150309</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="I4" s="1">
+      <c r="I4" s="72">
         <v>3138174050</v>
       </c>
-      <c r="J4" s="1" t="s">
-        <v>73</v>
+      <c r="J4" s="72" t="s">
+        <v>155</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>3</v>
+      <c r="A5" s="2">
+        <v>1098774228</v>
       </c>
       <c r="B5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>61</v>
+        <v>132</v>
       </c>
       <c r="D5" s="1">
         <v>3014187370</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="H5" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="H5" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="I5" s="1">
+      <c r="I5" s="72">
         <v>3138174050</v>
       </c>
-      <c r="J5" s="1" t="s">
-        <v>73</v>
+      <c r="J5" s="72" t="s">
+        <v>155</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>57</v>
+        <v>128</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>3</v>
+      <c r="A6" s="2">
+        <v>74083945</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D6" s="1">
         <v>3208495340</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="H6" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H6" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="I6" s="1">
+      <c r="I6" s="72">
         <v>3138174050</v>
       </c>
-      <c r="J6" s="1" t="s">
-        <v>73</v>
+      <c r="J6" s="72" t="s">
+        <v>155</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>62</v>
+        <v>133</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>3</v>
+      <c r="A7" s="2">
+        <v>1035854640</v>
       </c>
       <c r="B7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>61</v>
+        <v>132</v>
       </c>
       <c r="D7" s="1">
         <v>3228990545</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="I7" s="1">
+      <c r="I7" s="72">
         <v>3138174050</v>
       </c>
-      <c r="J7" s="1" t="s">
-        <v>73</v>
+      <c r="J7" s="72" t="s">
+        <v>155</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>3</v>
+      <c r="A8" s="2">
+        <v>80794172</v>
       </c>
       <c r="B8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D8" s="1">
         <v>3142421019</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="H8" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="H8" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="I8" s="1">
+      <c r="I8" s="72">
         <v>3138174050</v>
       </c>
-      <c r="J8" s="1" t="s">
-        <v>73</v>
+      <c r="J8" s="72" t="s">
+        <v>155</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>65</v>
+        <v>136</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>3</v>
+      <c r="A9" s="2">
+        <v>1019133012</v>
       </c>
       <c r="B9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>61</v>
+        <v>132</v>
       </c>
       <c r="D9" s="1">
         <v>3128894731</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="H9" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="H9" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="I9" s="1">
+      <c r="I9" s="72">
         <v>3138174050</v>
       </c>
-      <c r="J9" s="1" t="s">
-        <v>73</v>
+      <c r="J9" s="72" t="s">
+        <v>155</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>63</v>
+        <v>134</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>3</v>
+      <c r="A10" s="2">
+        <v>1019152161</v>
       </c>
       <c r="B10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>61</v>
+        <v>132</v>
       </c>
       <c r="D10" s="1">
         <v>3178958725</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="H10" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="H10" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="I10" s="1">
+      <c r="I10" s="72">
         <v>3138174050</v>
       </c>
-      <c r="J10" s="1" t="s">
-        <v>73</v>
+      <c r="J10" s="72" t="s">
+        <v>155</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>58</v>
+        <v>129</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>3</v>
+      <c r="A11" s="2">
+        <v>1082898312</v>
       </c>
       <c r="B11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D11" s="1">
         <v>3015001273</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="I11" s="1">
+      <c r="I11" s="72">
         <v>3138174050</v>
       </c>
-      <c r="J11" s="1" t="s">
-        <v>73</v>
+      <c r="J11" s="72" t="s">
+        <v>155</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>72</v>
+        <v>154</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>3</v>
+      <c r="A12" s="2">
+        <v>83168382</v>
       </c>
       <c r="B12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D12" s="1">
         <v>3152946638</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="I12" s="1">
+      <c r="I12" s="72">
         <v>3138174050</v>
       </c>
-      <c r="J12" s="1" t="s">
-        <v>73</v>
+      <c r="J12" s="72" t="s">
+        <v>155</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>66</v>
+        <v>137</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>3</v>
+      <c r="A13" s="2">
+        <v>1075213439</v>
       </c>
       <c r="B13" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>61</v>
+        <v>132</v>
       </c>
       <c r="D13" s="1">
         <v>3204432121</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="I13" s="1">
+      <c r="I13" s="72">
         <v>3138174050</v>
       </c>
-      <c r="J13" s="1" t="s">
-        <v>73</v>
+      <c r="J13" s="72" t="s">
+        <v>155</v>
       </c>
       <c r="K13" s="2" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>3</v>
+      <c r="A14" s="2">
+        <v>1233890099</v>
       </c>
       <c r="B14" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>61</v>
+        <v>132</v>
       </c>
       <c r="D14" s="1">
         <v>3057670925</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H14" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="I14" s="1">
+      <c r="I14" s="72">
         <v>3138174050</v>
       </c>
-      <c r="J14" s="1" t="s">
-        <v>73</v>
+      <c r="J14" s="72" t="s">
+        <v>155</v>
       </c>
       <c r="K14" s="2" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>3</v>
+      <c r="A15" s="2">
+        <v>1018408231</v>
       </c>
       <c r="B15" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D15" s="1">
         <v>3176963137</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H15" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="H15" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="I15" s="1">
+      <c r="I15" s="72">
         <v>3138174050</v>
       </c>
-      <c r="J15" s="1" t="s">
-        <v>73</v>
+      <c r="J15" s="72" t="s">
+        <v>155</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>64</v>
+        <v>135</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>3</v>
+      <c r="A16" s="2">
+        <v>1017222178</v>
       </c>
       <c r="B16" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>61</v>
+        <v>132</v>
       </c>
       <c r="D16" s="1">
         <v>3202818282</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H16" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="I16" s="1">
+      <c r="I16" s="72">
         <v>3138174050</v>
       </c>
-      <c r="J16" s="1" t="s">
-        <v>73</v>
+      <c r="J16" s="72" t="s">
+        <v>155</v>
       </c>
       <c r="K16" s="2" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>3</v>
+      <c r="A17" s="2">
+        <v>1075276712</v>
       </c>
       <c r="B17" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>61</v>
+        <v>132</v>
       </c>
       <c r="D17" s="1">
         <v>3157939923</v>
       </c>
       <c r="E17" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G17" s="3" t="s">
         <v>43</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>42</v>
       </c>
       <c r="H17" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="I17" s="1">
+      <c r="I17" s="72">
         <v>3138174050</v>
       </c>
-      <c r="J17" s="1" t="s">
-        <v>73</v>
+      <c r="J17" s="72" t="s">
+        <v>155</v>
       </c>
       <c r="K17" s="3"/>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>3</v>
+      <c r="A18" s="2">
+        <v>1075250696</v>
       </c>
       <c r="B18" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D18" s="1">
         <v>3187826413</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H18" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H18" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="I18" s="1">
+      <c r="I18" s="72">
         <v>3138174050</v>
       </c>
-      <c r="J18" s="1" t="s">
-        <v>73</v>
+      <c r="J18" s="72" t="s">
+        <v>155</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>60</v>
+        <v>131</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>3</v>
+      <c r="A19" s="2">
+        <v>1098728440</v>
       </c>
       <c r="B19" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D19" s="1">
         <v>3176801825</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H19" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="I19" s="1">
+      <c r="I19" s="72">
         <v>3138174050</v>
       </c>
-      <c r="J19" s="1" t="s">
-        <v>73</v>
+      <c r="J19" s="72" t="s">
+        <v>155</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>67</v>
+        <v>138</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
-        <v>3</v>
+      <c r="A20" s="2">
+        <v>1098712563</v>
       </c>
       <c r="B20" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>61</v>
+        <v>132</v>
       </c>
       <c r="D20" s="1">
         <v>3013715669</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H20" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="I20" s="1">
+      <c r="I20" s="72">
         <v>3138174050</v>
       </c>
-      <c r="J20" s="1" t="s">
-        <v>73</v>
+      <c r="J20" s="72" t="s">
+        <v>155</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>59</v>
+        <v>130</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
-        <v>3</v>
+      <c r="A21" s="2">
+        <v>1075248439</v>
       </c>
       <c r="B21" t="s">
-        <v>70</v>
+        <v>141</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D21" s="1">
         <v>3107656528</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H21" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="I21" s="1">
+      <c r="I21" s="72">
         <v>3138174050</v>
       </c>
-      <c r="J21" s="1" t="s">
-        <v>73</v>
+      <c r="J21" s="72" t="s">
+        <v>155</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>71</v>
-      </c>
+        <v>142</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="G29" s="70"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="G6" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="G11" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="G18" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="G15" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="G2" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="G5" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="G20" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="G16" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="G7" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="G10" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
-    <hyperlink ref="G14" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
-    <hyperlink ref="G17" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="G4" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
-    <hyperlink ref="G3" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
-    <hyperlink ref="G13" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
-    <hyperlink ref="G8" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="G19" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
-    <hyperlink ref="G12" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
-    <hyperlink ref="G9" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
-    <hyperlink ref="K5" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
-    <hyperlink ref="K10" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
-    <hyperlink ref="K20" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
-    <hyperlink ref="K18" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
-    <hyperlink ref="K6" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
-    <hyperlink ref="K9" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
-    <hyperlink ref="K15" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
-    <hyperlink ref="K8" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
-    <hyperlink ref="K12" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
-    <hyperlink ref="K19" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
-    <hyperlink ref="K3" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
-    <hyperlink ref="K2" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
-    <hyperlink ref="K21" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
-    <hyperlink ref="G21" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
-    <hyperlink ref="K11" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
+    <hyperlink ref="G6" r:id="rId1"/>
+    <hyperlink ref="G11" r:id="rId2"/>
+    <hyperlink ref="G18" r:id="rId3"/>
+    <hyperlink ref="G15" r:id="rId4"/>
+    <hyperlink ref="G2" r:id="rId5"/>
+    <hyperlink ref="G5" r:id="rId6"/>
+    <hyperlink ref="G20" r:id="rId7"/>
+    <hyperlink ref="G16" r:id="rId8"/>
+    <hyperlink ref="G7" r:id="rId9"/>
+    <hyperlink ref="G10" r:id="rId10"/>
+    <hyperlink ref="G14" r:id="rId11"/>
+    <hyperlink ref="G17" r:id="rId12"/>
+    <hyperlink ref="G4" r:id="rId13"/>
+    <hyperlink ref="G3" r:id="rId14"/>
+    <hyperlink ref="G13" r:id="rId15"/>
+    <hyperlink ref="G8" r:id="rId16"/>
+    <hyperlink ref="G19" r:id="rId17"/>
+    <hyperlink ref="G12" r:id="rId18"/>
+    <hyperlink ref="G9" r:id="rId19"/>
+    <hyperlink ref="K5" r:id="rId20"/>
+    <hyperlink ref="K10" r:id="rId21"/>
+    <hyperlink ref="K20" r:id="rId22"/>
+    <hyperlink ref="K18" r:id="rId23"/>
+    <hyperlink ref="K6" r:id="rId24"/>
+    <hyperlink ref="K9" r:id="rId25"/>
+    <hyperlink ref="K15" r:id="rId26"/>
+    <hyperlink ref="K8" r:id="rId27"/>
+    <hyperlink ref="K12" r:id="rId28"/>
+    <hyperlink ref="K19" r:id="rId29"/>
+    <hyperlink ref="K3" r:id="rId30"/>
+    <hyperlink ref="K2" r:id="rId31"/>
+    <hyperlink ref="K21" r:id="rId32"/>
+    <hyperlink ref="G21" r:id="rId33"/>
+    <hyperlink ref="K11" r:id="rId34"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId35"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:H135"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="41.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="63.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="29.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A3" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A10" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A11" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A12" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A15" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A16" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="B16" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A18" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="C18" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="D18" s="11" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A20" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A23" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="B23" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="C23" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="D23" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="H23" s="26"/>
+    </row>
+    <row r="24" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="B28" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="C28" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="D34" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A35" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B35" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="C35" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="D35" s="9" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A36" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="B36" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="C36" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="D36" s="11" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A37" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="B37" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="C37" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="D37" s="9" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A38" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B38" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="C38" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="D38" s="9" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A39" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="B39" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="C39" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="D39" s="9" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A40" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B40" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="C40" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="D40" s="9" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A41" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="B41" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="C41" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="D41" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A42" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B42" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="C42" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="D42" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A43" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="B43" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="C43" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="D43" s="11" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A44" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="B44" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="C44" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="D44" s="11" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A45" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="B45" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="C45" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="D45" s="11" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A46" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="B46" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="C46" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="D46" s="11" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A47" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="B47" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="C47" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="D47" s="11" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A48" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="B48" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="C48" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="D48" s="11" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A49" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="B49" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="C49" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="D49" s="11" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A50" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B50" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="C50" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="D50" s="9" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A51" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="B51" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="C51" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="D51" s="11" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A52" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B52" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="C52" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="D52" s="9" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A53" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="B53" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="C53" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="D53" s="16" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A54" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="B54" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="C54" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="D54" s="11" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A55" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="B55" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="C55" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="D55" s="11" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="B56" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="C56" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="D56" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A57" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="B57" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="C57" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="D57" s="9" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A58" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="B58" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="C58" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="D58" s="9" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A59" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="B59" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="C59" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="D59" s="9" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A60" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="B60" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="C60" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="D60" s="9" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A61" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="B61" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="C61" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="D61" s="9" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A62" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="B62" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="C62" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="D62" s="11" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A63" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="B63" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="C63" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="D63" s="11" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A64" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="B64" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="C64" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="D64" s="11" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A65" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="B65" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="C65" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="D65" s="11" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="B66" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="C66" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="D66" s="7" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="B67" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="C67" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="D67" s="7" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A68" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="B68" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="C68" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="D68" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="B69" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="C69" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="D69" s="7" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="B70" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="C70" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="D70" s="7" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A71" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="B71" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="C71" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="D71" s="9" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="B72" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="C72" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="D72" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="B73" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="C73" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="D73" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="B74" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="C74" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="D74" s="7" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A75" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="B75" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="C75" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="D75" s="11" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A76" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B76" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="C76" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="D76" s="7" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A77" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="B77" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="C77" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="D77" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A78" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B78" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="C78" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="D78" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A79" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="B79" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="C79" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="D79" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A80" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B80" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="C80" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="D80" s="7" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A81" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="B81" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="C81" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="D81" s="9" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A82" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B82" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="C82" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="D82" s="7" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A83" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="B83" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="C83" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="D83" s="11" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A84" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B84" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="C84" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="D84" s="7" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A85" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="B85" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="C85" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="D85" s="9" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A86" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="B86" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="C86" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="D86" s="11" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A87" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="B87" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="C87" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="D87" s="7" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A88" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B88" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="C88" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="D88" s="9" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A89" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B89" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="C89" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="D89" s="11" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A90" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B90" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C90" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="D90" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A91" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="B91" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="C91" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="D91" s="11" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A92" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B92" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="C92" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="D92" s="11" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A93" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B93" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C93" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="D93" s="7" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A94" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="B94" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="C94" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D94" s="7" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A95" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="B95" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="C95" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="D95" s="7" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A96" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="B96" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="C96" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="D96" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A97" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="B97" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="C97" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D97" s="7" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A98" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B98" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="C98" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="D98" s="7" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A99" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="B99" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="C99" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="D99" s="9" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A100" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B100" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="C100" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="D100" s="9" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A101" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="B101" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="C101" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="D101" s="11" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A102" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B102" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="C102" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="D102" s="11" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A103" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B103" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="C103" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D103" s="7" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A104" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B104" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="C104" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="D104" s="11" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A105" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="B105" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="C105" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="D105" s="11" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A106" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B106" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="C106" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D106" s="7" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A107" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="B107" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="C107" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="D107" s="7" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A110" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="B110" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A111" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="B111" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A112" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="B112" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A113" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="B113" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A114" s="19" t="s">
+        <v>68</v>
+      </c>
+      <c r="B114" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A115" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="B115" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A116" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="B116" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A117" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="B117" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A118" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="B118" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A119" s="19" t="s">
+        <v>49</v>
+      </c>
+      <c r="B119" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A120" s="19" t="s">
+        <v>49</v>
+      </c>
+      <c r="B120" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A121" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="B121" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A122" s="21" t="s">
+        <v>101</v>
+      </c>
+      <c r="B122" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A123" s="22" t="s">
+        <v>32</v>
+      </c>
+      <c r="B123" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A124" s="23" t="s">
+        <v>79</v>
+      </c>
+      <c r="B124" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A125" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="B125" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A126" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="B126" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A127" s="22" t="s">
+        <v>61</v>
+      </c>
+      <c r="B127" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A128" s="22" t="s">
+        <v>77</v>
+      </c>
+      <c r="B128" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A129" s="22" t="s">
+        <v>85</v>
+      </c>
+      <c r="B129" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A130" s="22" t="s">
+        <v>91</v>
+      </c>
+      <c r="B130" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A131" s="22" t="s">
+        <v>99</v>
+      </c>
+      <c r="B131" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A132" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="B132" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A133" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="B133" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A134" s="22" t="s">
+        <v>92</v>
+      </c>
+      <c r="B134" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A135" s="24"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:D107"/>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B107">
+      <formula1>INDIRECT(AD2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ERROR" error="Escriba nuevamente" promptTitle="Ingrese el Personal" sqref="A1:A107 H23 A110:A134">
+      <formula1>#REF!</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F67"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="41.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="39.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="42" t="s">
+        <v>57</v>
+      </c>
+      <c r="B1" s="43" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1" s="44" t="s">
+        <v>60</v>
+      </c>
+      <c r="D1" s="43" t="s">
+        <v>143</v>
+      </c>
+      <c r="E1" s="45" t="s">
+        <v>144</v>
+      </c>
+      <c r="F1" s="45" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="46" t="s">
+        <v>83</v>
+      </c>
+      <c r="B2" s="47" t="s">
+        <v>70</v>
+      </c>
+      <c r="C2" s="47" t="s">
+        <v>64</v>
+      </c>
+      <c r="D2" s="48">
+        <v>45677</v>
+      </c>
+      <c r="E2" s="49">
+        <v>45692</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A3" s="50" t="s">
+        <v>83</v>
+      </c>
+      <c r="B3" s="32" t="s">
+        <v>70</v>
+      </c>
+      <c r="C3" s="32" t="s">
+        <v>67</v>
+      </c>
+      <c r="D3" s="33">
+        <v>45702</v>
+      </c>
+      <c r="E3" s="51">
+        <v>45709</v>
+      </c>
+      <c r="F3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="50" t="s">
+        <v>83</v>
+      </c>
+      <c r="B4" s="32" t="s">
+        <v>70</v>
+      </c>
+      <c r="C4" s="32" t="s">
+        <v>74</v>
+      </c>
+      <c r="D4" s="33">
+        <v>45724</v>
+      </c>
+      <c r="E4" s="51">
+        <v>45736</v>
+      </c>
+      <c r="F4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="50" t="s">
+        <v>83</v>
+      </c>
+      <c r="B5" s="32" t="s">
+        <v>70</v>
+      </c>
+      <c r="C5" s="32" t="s">
+        <v>75</v>
+      </c>
+      <c r="D5" s="33">
+        <v>45752</v>
+      </c>
+      <c r="E5" s="51">
+        <v>45764</v>
+      </c>
+      <c r="F5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="50" t="s">
+        <v>83</v>
+      </c>
+      <c r="B6" s="32" t="s">
+        <v>65</v>
+      </c>
+      <c r="C6" s="32" t="s">
+        <v>76</v>
+      </c>
+      <c r="D6" s="33">
+        <v>45778</v>
+      </c>
+      <c r="E6" s="51">
+        <v>45790</v>
+      </c>
+      <c r="F6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="50" t="s">
+        <v>83</v>
+      </c>
+      <c r="B7" s="32" t="s">
+        <v>65</v>
+      </c>
+      <c r="C7" s="32" t="s">
+        <v>87</v>
+      </c>
+      <c r="D7" s="36">
+        <v>45805</v>
+      </c>
+      <c r="E7" s="51">
+        <v>45816</v>
+      </c>
+      <c r="F7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="52" t="s">
+        <v>83</v>
+      </c>
+      <c r="B8" s="28" t="s">
+        <v>65</v>
+      </c>
+      <c r="C8" s="28" t="s">
+        <v>88</v>
+      </c>
+      <c r="D8" s="29">
+        <v>45837</v>
+      </c>
+      <c r="E8" s="53">
+        <v>45850</v>
+      </c>
+      <c r="F8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="46" t="s">
+        <v>34</v>
+      </c>
+      <c r="B9" s="47" t="s">
+        <v>71</v>
+      </c>
+      <c r="C9" s="47" t="s">
+        <v>67</v>
+      </c>
+      <c r="D9" s="48">
+        <v>45702</v>
+      </c>
+      <c r="E9" s="49">
+        <v>45716</v>
+      </c>
+      <c r="F9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A10" s="50" t="s">
+        <v>34</v>
+      </c>
+      <c r="B10" s="32" t="s">
+        <v>71</v>
+      </c>
+      <c r="C10" s="32" t="s">
+        <v>74</v>
+      </c>
+      <c r="D10" s="36">
+        <v>45730</v>
+      </c>
+      <c r="E10" s="51">
+        <v>45741</v>
+      </c>
+      <c r="F10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A11" s="50" t="s">
+        <v>34</v>
+      </c>
+      <c r="B11" s="32" t="s">
+        <v>71</v>
+      </c>
+      <c r="C11" s="32" t="s">
+        <v>75</v>
+      </c>
+      <c r="D11" s="36">
+        <v>45755</v>
+      </c>
+      <c r="E11" s="51">
+        <v>45769</v>
+      </c>
+      <c r="F11">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A12" s="50" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12" s="32" t="s">
+        <v>71</v>
+      </c>
+      <c r="C12" s="32" t="s">
+        <v>76</v>
+      </c>
+      <c r="D12" s="36">
+        <v>45783</v>
+      </c>
+      <c r="E12" s="51">
+        <v>45797</v>
+      </c>
+      <c r="F12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A13" s="50" t="s">
+        <v>34</v>
+      </c>
+      <c r="B13" s="32" t="s">
+        <v>71</v>
+      </c>
+      <c r="C13" s="32" t="s">
+        <v>87</v>
+      </c>
+      <c r="D13" s="36">
+        <v>45811</v>
+      </c>
+      <c r="E13" s="51">
+        <v>45825</v>
+      </c>
+      <c r="F13">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A14" s="50" t="s">
+        <v>34</v>
+      </c>
+      <c r="B14" s="32" t="s">
+        <v>71</v>
+      </c>
+      <c r="C14" s="32" t="s">
+        <v>88</v>
+      </c>
+      <c r="D14" s="33">
+        <v>45853</v>
+      </c>
+      <c r="E14" s="51">
+        <v>45867</v>
+      </c>
+      <c r="F14">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="52" t="s">
+        <v>34</v>
+      </c>
+      <c r="B15" s="28" t="s">
+        <v>71</v>
+      </c>
+      <c r="C15" s="28" t="s">
+        <v>93</v>
+      </c>
+      <c r="D15" s="34">
+        <v>45881</v>
+      </c>
+      <c r="E15" s="54">
+        <v>45895</v>
+      </c>
+      <c r="F15">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A16" s="46" t="s">
+        <v>97</v>
+      </c>
+      <c r="B16" s="47" t="s">
+        <v>71</v>
+      </c>
+      <c r="C16" s="47" t="s">
+        <v>67</v>
+      </c>
+      <c r="D16" s="55">
+        <v>45695</v>
+      </c>
+      <c r="E16" s="49">
+        <v>45709</v>
+      </c>
+      <c r="F16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="52" t="s">
+        <v>97</v>
+      </c>
+      <c r="B17" s="28" t="s">
+        <v>71</v>
+      </c>
+      <c r="C17" s="28" t="s">
+        <v>74</v>
+      </c>
+      <c r="D17" s="34">
+        <v>45723</v>
+      </c>
+      <c r="E17" s="54">
+        <v>45736</v>
+      </c>
+      <c r="F17">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A18" s="56" t="s">
+        <v>97</v>
+      </c>
+      <c r="B18" s="39" t="s">
+        <v>71</v>
+      </c>
+      <c r="C18" s="39" t="s">
+        <v>76</v>
+      </c>
+      <c r="D18" s="41">
+        <v>45797</v>
+      </c>
+      <c r="E18" s="57">
+        <v>45811</v>
+      </c>
+      <c r="F18">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A19" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="B19" s="32" t="s">
+        <v>71</v>
+      </c>
+      <c r="C19" s="32" t="s">
+        <v>87</v>
+      </c>
+      <c r="D19" s="33">
+        <v>45825</v>
+      </c>
+      <c r="E19" s="51">
+        <v>45839</v>
+      </c>
+      <c r="F19">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A20" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="B20" s="32" t="s">
+        <v>71</v>
+      </c>
+      <c r="C20" s="32" t="s">
+        <v>88</v>
+      </c>
+      <c r="D20" s="33">
+        <v>45853</v>
+      </c>
+      <c r="E20" s="51">
+        <v>45867</v>
+      </c>
+      <c r="F20">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A21" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="B21" s="32" t="s">
+        <v>71</v>
+      </c>
+      <c r="C21" s="32" t="s">
+        <v>93</v>
+      </c>
+      <c r="D21" s="33">
+        <v>45881</v>
+      </c>
+      <c r="E21" s="51">
+        <v>45895</v>
+      </c>
+      <c r="F21">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="52" t="s">
+        <v>97</v>
+      </c>
+      <c r="B22" s="28" t="s">
+        <v>71</v>
+      </c>
+      <c r="C22" s="28" t="s">
+        <v>94</v>
+      </c>
+      <c r="D22" s="34">
+        <v>45909</v>
+      </c>
+      <c r="E22" s="54">
+        <v>45923</v>
+      </c>
+      <c r="F22">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A23" s="46" t="s">
+        <v>40</v>
+      </c>
+      <c r="B23" s="47" t="s">
+        <v>73</v>
+      </c>
+      <c r="C23" s="47" t="s">
+        <v>64</v>
+      </c>
+      <c r="D23" s="48">
+        <v>45681</v>
+      </c>
+      <c r="E23" s="49">
+        <v>45695</v>
+      </c>
+      <c r="F23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A24" s="50" t="s">
+        <v>40</v>
+      </c>
+      <c r="B24" s="32" t="s">
+        <v>73</v>
+      </c>
+      <c r="C24" s="32" t="s">
+        <v>67</v>
+      </c>
+      <c r="D24" s="33">
+        <v>45709</v>
+      </c>
+      <c r="E24" s="51">
+        <v>45723</v>
+      </c>
+      <c r="F24">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A25" s="50" t="s">
+        <v>40</v>
+      </c>
+      <c r="B25" s="32" t="s">
+        <v>73</v>
+      </c>
+      <c r="C25" s="32" t="s">
+        <v>74</v>
+      </c>
+      <c r="D25" s="33">
+        <v>45734</v>
+      </c>
+      <c r="E25" s="51">
+        <v>45743</v>
+      </c>
+      <c r="F25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="52" t="s">
+        <v>40</v>
+      </c>
+      <c r="B26" s="28" t="s">
+        <v>73</v>
+      </c>
+      <c r="C26" s="28" t="s">
+        <v>145</v>
+      </c>
+      <c r="D26" s="34">
+        <v>45776</v>
+      </c>
+      <c r="E26" s="54">
+        <v>45790</v>
+      </c>
+      <c r="F26" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A27" s="56" t="s">
+        <v>101</v>
+      </c>
+      <c r="B27" s="39" t="s">
+        <v>62</v>
+      </c>
+      <c r="C27" s="39" t="s">
+        <v>64</v>
+      </c>
+      <c r="D27" s="40">
+        <v>45688</v>
+      </c>
+      <c r="E27" s="57">
+        <v>45702</v>
+      </c>
+      <c r="F27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A28" s="50" t="s">
+        <v>101</v>
+      </c>
+      <c r="B28" s="32" t="s">
+        <v>62</v>
+      </c>
+      <c r="C28" s="32" t="s">
+        <v>67</v>
+      </c>
+      <c r="D28" s="36">
+        <v>45716</v>
+      </c>
+      <c r="E28" s="51">
+        <v>45727</v>
+      </c>
+      <c r="F28">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="52" t="s">
+        <v>101</v>
+      </c>
+      <c r="B29" s="28" t="s">
+        <v>62</v>
+      </c>
+      <c r="C29" s="28" t="s">
+        <v>74</v>
+      </c>
+      <c r="D29" s="29">
+        <v>45734</v>
+      </c>
+      <c r="E29" s="54">
+        <v>45741</v>
+      </c>
+      <c r="F29">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="58" t="s">
+        <v>32</v>
+      </c>
+      <c r="B30" s="37" t="s">
+        <v>73</v>
+      </c>
+      <c r="C30" s="37" t="s">
+        <v>115</v>
+      </c>
+      <c r="D30" s="38">
+        <v>45709</v>
+      </c>
+      <c r="E30" s="59">
+        <v>45723</v>
+      </c>
+      <c r="F30" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A31" s="46" t="s">
+        <v>11</v>
+      </c>
+      <c r="B31" s="47" t="s">
+        <v>71</v>
+      </c>
+      <c r="C31" s="47" t="s">
+        <v>64</v>
+      </c>
+      <c r="D31" s="48">
+        <v>45667</v>
+      </c>
+      <c r="E31" s="60">
+        <v>45681</v>
+      </c>
+      <c r="F31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A32" s="50" t="s">
+        <v>11</v>
+      </c>
+      <c r="B32" s="32" t="s">
+        <v>71</v>
+      </c>
+      <c r="C32" s="32" t="s">
+        <v>67</v>
+      </c>
+      <c r="D32" s="33">
+        <v>45695</v>
+      </c>
+      <c r="E32" s="51">
+        <v>45709</v>
+      </c>
+      <c r="F32">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A33" s="50" t="s">
+        <v>11</v>
+      </c>
+      <c r="B33" s="32" t="s">
+        <v>71</v>
+      </c>
+      <c r="C33" s="32" t="s">
+        <v>74</v>
+      </c>
+      <c r="D33" s="33">
+        <v>45723</v>
+      </c>
+      <c r="E33" s="51">
+        <v>45734</v>
+      </c>
+      <c r="F33">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="52" t="s">
+        <v>11</v>
+      </c>
+      <c r="B34" s="28" t="s">
+        <v>71</v>
+      </c>
+      <c r="C34" s="28" t="s">
+        <v>75</v>
+      </c>
+      <c r="D34" s="35">
+        <v>45743</v>
+      </c>
+      <c r="E34" s="61">
+        <v>45752</v>
+      </c>
+      <c r="F34">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A35" s="46" t="s">
+        <v>85</v>
+      </c>
+      <c r="B35" s="47" t="s">
+        <v>70</v>
+      </c>
+      <c r="C35" s="47" t="s">
+        <v>67</v>
+      </c>
+      <c r="D35" s="48">
+        <v>45692</v>
+      </c>
+      <c r="E35" s="49">
+        <v>45702</v>
+      </c>
+      <c r="F35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A36" s="50" t="s">
+        <v>85</v>
+      </c>
+      <c r="B36" s="32" t="s">
+        <v>70</v>
+      </c>
+      <c r="C36" s="32" t="s">
+        <v>74</v>
+      </c>
+      <c r="D36" s="33">
+        <v>45709</v>
+      </c>
+      <c r="E36" s="51">
+        <v>45724</v>
+      </c>
+      <c r="F36">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A37" s="50" t="s">
+        <v>85</v>
+      </c>
+      <c r="B37" s="32" t="s">
+        <v>70</v>
+      </c>
+      <c r="C37" s="32" t="s">
+        <v>75</v>
+      </c>
+      <c r="D37" s="33">
+        <v>45736</v>
+      </c>
+      <c r="E37" s="51">
+        <v>45753</v>
+      </c>
+      <c r="F37">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="52" t="s">
+        <v>85</v>
+      </c>
+      <c r="B38" s="28" t="s">
+        <v>70</v>
+      </c>
+      <c r="C38" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="D38" s="34">
+        <v>45790</v>
+      </c>
+      <c r="E38" s="54">
+        <v>45804</v>
+      </c>
+      <c r="F38">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A39" s="46" t="s">
+        <v>91</v>
+      </c>
+      <c r="B39" s="47" t="s">
+        <v>71</v>
+      </c>
+      <c r="C39" s="47" t="s">
+        <v>64</v>
+      </c>
+      <c r="D39" s="48">
+        <v>45685</v>
+      </c>
+      <c r="E39" s="49">
+        <v>45702</v>
+      </c>
+      <c r="F39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A40" s="50" t="s">
+        <v>91</v>
+      </c>
+      <c r="B40" s="32" t="s">
+        <v>71</v>
+      </c>
+      <c r="C40" s="32" t="s">
+        <v>67</v>
+      </c>
+      <c r="D40" s="36">
+        <v>45716</v>
+      </c>
+      <c r="E40" s="51">
+        <v>45730</v>
+      </c>
+      <c r="F40">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A41" s="50" t="s">
+        <v>91</v>
+      </c>
+      <c r="B41" s="32" t="s">
+        <v>71</v>
+      </c>
+      <c r="C41" s="32" t="s">
+        <v>74</v>
+      </c>
+      <c r="D41" s="36">
+        <v>45741</v>
+      </c>
+      <c r="E41" s="51">
+        <v>45755</v>
+      </c>
+      <c r="F41">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A42" s="50" t="s">
+        <v>91</v>
+      </c>
+      <c r="B42" s="32" t="s">
+        <v>71</v>
+      </c>
+      <c r="C42" s="32" t="s">
+        <v>75</v>
+      </c>
+      <c r="D42" s="33">
+        <v>45769</v>
+      </c>
+      <c r="E42" s="51">
+        <v>45783</v>
+      </c>
+      <c r="F42">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="62" t="s">
+        <v>91</v>
+      </c>
+      <c r="B43" s="30" t="s">
+        <v>71</v>
+      </c>
+      <c r="C43" s="30" t="s">
+        <v>146</v>
+      </c>
+      <c r="D43" s="31">
+        <v>45797</v>
+      </c>
+      <c r="E43" s="63">
+        <v>45811</v>
+      </c>
+      <c r="F43" s="69" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A44" s="46" t="s">
+        <v>99</v>
+      </c>
+      <c r="B44" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="C44" s="47" t="s">
+        <v>64</v>
+      </c>
+      <c r="D44" s="48">
+        <v>45673</v>
+      </c>
+      <c r="E44" s="49">
+        <v>45688</v>
+      </c>
+      <c r="F44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A45" s="50" t="s">
+        <v>99</v>
+      </c>
+      <c r="B45" s="32" t="s">
+        <v>62</v>
+      </c>
+      <c r="C45" s="32" t="s">
+        <v>67</v>
+      </c>
+      <c r="D45" s="36">
+        <v>45702</v>
+      </c>
+      <c r="E45" s="51">
+        <v>45716</v>
+      </c>
+      <c r="F45">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A46" s="50" t="s">
+        <v>99</v>
+      </c>
+      <c r="B46" s="32" t="s">
+        <v>62</v>
+      </c>
+      <c r="C46" s="32" t="s">
+        <v>74</v>
+      </c>
+      <c r="D46" s="36">
+        <v>45727</v>
+      </c>
+      <c r="E46" s="51">
+        <v>45734</v>
+      </c>
+      <c r="F46">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A47" s="50" t="s">
+        <v>99</v>
+      </c>
+      <c r="B47" s="32" t="s">
+        <v>71</v>
+      </c>
+      <c r="C47" s="32" t="s">
+        <v>75</v>
+      </c>
+      <c r="D47" s="33">
+        <v>45783</v>
+      </c>
+      <c r="E47" s="51">
+        <v>45797</v>
+      </c>
+      <c r="F47">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A48" s="50" t="s">
+        <v>99</v>
+      </c>
+      <c r="B48" s="32" t="s">
+        <v>71</v>
+      </c>
+      <c r="C48" s="32" t="s">
+        <v>76</v>
+      </c>
+      <c r="D48" s="33">
+        <v>45811</v>
+      </c>
+      <c r="E48" s="51">
+        <v>45825</v>
+      </c>
+      <c r="F48">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A49" s="50" t="s">
+        <v>99</v>
+      </c>
+      <c r="B49" s="32" t="s">
+        <v>71</v>
+      </c>
+      <c r="C49" s="32" t="s">
+        <v>87</v>
+      </c>
+      <c r="D49" s="33">
+        <v>45839</v>
+      </c>
+      <c r="E49" s="51">
+        <v>45853</v>
+      </c>
+      <c r="F49">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A50" s="50" t="s">
+        <v>99</v>
+      </c>
+      <c r="B50" s="32" t="s">
+        <v>71</v>
+      </c>
+      <c r="C50" s="32" t="s">
+        <v>88</v>
+      </c>
+      <c r="D50" s="33">
+        <v>45867</v>
+      </c>
+      <c r="E50" s="51">
+        <v>45881</v>
+      </c>
+      <c r="F50">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="52" t="s">
+        <v>99</v>
+      </c>
+      <c r="B51" s="28" t="s">
+        <v>71</v>
+      </c>
+      <c r="C51" s="28" t="s">
+        <v>120</v>
+      </c>
+      <c r="D51" s="34">
+        <v>45895</v>
+      </c>
+      <c r="E51" s="54">
+        <v>45909</v>
+      </c>
+      <c r="F51" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A52" s="56" t="s">
+        <v>30</v>
+      </c>
+      <c r="B52" s="39" t="s">
+        <v>71</v>
+      </c>
+      <c r="C52" s="39" t="s">
+        <v>64</v>
+      </c>
+      <c r="D52" s="40">
+        <v>45674</v>
+      </c>
+      <c r="E52" s="64">
+        <v>45688</v>
+      </c>
+      <c r="F52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A53" s="50" t="s">
+        <v>30</v>
+      </c>
+      <c r="B53" s="32" t="s">
+        <v>71</v>
+      </c>
+      <c r="C53" s="32" t="s">
+        <v>67</v>
+      </c>
+      <c r="D53" s="36">
+        <v>45702</v>
+      </c>
+      <c r="E53" s="51">
+        <v>45716</v>
+      </c>
+      <c r="F53">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A54" s="50" t="s">
+        <v>30</v>
+      </c>
+      <c r="B54" s="32" t="s">
+        <v>71</v>
+      </c>
+      <c r="C54" s="32" t="s">
+        <v>74</v>
+      </c>
+      <c r="D54" s="36">
+        <v>45730</v>
+      </c>
+      <c r="E54" s="51">
+        <v>45741</v>
+      </c>
+      <c r="F54">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A55" s="50" t="s">
+        <v>30</v>
+      </c>
+      <c r="B55" s="32" t="s">
+        <v>71</v>
+      </c>
+      <c r="C55" s="32" t="s">
+        <v>75</v>
+      </c>
+      <c r="D55" s="36">
+        <v>45755</v>
+      </c>
+      <c r="E55" s="51">
+        <v>45769</v>
+      </c>
+      <c r="F55">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A56" s="50" t="s">
+        <v>30</v>
+      </c>
+      <c r="B56" s="32" t="s">
+        <v>71</v>
+      </c>
+      <c r="C56" s="32" t="s">
+        <v>76</v>
+      </c>
+      <c r="D56" s="33">
+        <v>45783</v>
+      </c>
+      <c r="E56" s="51">
+        <v>45797</v>
+      </c>
+      <c r="F56">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A57" s="50" t="s">
+        <v>30</v>
+      </c>
+      <c r="B57" s="32" t="s">
+        <v>71</v>
+      </c>
+      <c r="C57" s="32" t="s">
+        <v>87</v>
+      </c>
+      <c r="D57" s="33">
+        <v>45811</v>
+      </c>
+      <c r="E57" s="51">
+        <v>45825</v>
+      </c>
+      <c r="F57">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A58" s="50" t="s">
+        <v>30</v>
+      </c>
+      <c r="B58" s="32" t="s">
+        <v>71</v>
+      </c>
+      <c r="C58" s="32" t="s">
+        <v>88</v>
+      </c>
+      <c r="D58" s="33">
+        <v>45839</v>
+      </c>
+      <c r="E58" s="51">
+        <v>45853</v>
+      </c>
+      <c r="F58">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A59" s="50" t="s">
+        <v>30</v>
+      </c>
+      <c r="B59" s="32" t="s">
+        <v>71</v>
+      </c>
+      <c r="C59" s="32" t="s">
+        <v>93</v>
+      </c>
+      <c r="D59" s="33">
+        <v>45867</v>
+      </c>
+      <c r="E59" s="51">
+        <v>45881</v>
+      </c>
+      <c r="F59">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="62" t="s">
+        <v>30</v>
+      </c>
+      <c r="B60" s="30" t="s">
+        <v>71</v>
+      </c>
+      <c r="C60" s="30" t="s">
+        <v>94</v>
+      </c>
+      <c r="D60" s="31">
+        <v>45895</v>
+      </c>
+      <c r="E60" s="63">
+        <v>45909</v>
+      </c>
+      <c r="F60">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="65" t="s">
+        <v>30</v>
+      </c>
+      <c r="B61" s="66" t="s">
+        <v>71</v>
+      </c>
+      <c r="C61" s="66" t="s">
+        <v>96</v>
+      </c>
+      <c r="D61" s="67">
+        <v>46009</v>
+      </c>
+      <c r="E61" s="68">
+        <v>46022</v>
+      </c>
+      <c r="F61">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A62" s="46" t="s">
+        <v>92</v>
+      </c>
+      <c r="B62" s="47" t="s">
+        <v>71</v>
+      </c>
+      <c r="C62" s="47" t="s">
+        <v>147</v>
+      </c>
+      <c r="D62" s="48">
+        <v>45688</v>
+      </c>
+      <c r="E62" s="49">
+        <v>45702</v>
+      </c>
+      <c r="F62" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A63" s="50" t="s">
+        <v>92</v>
+      </c>
+      <c r="B63" s="32" t="s">
+        <v>71</v>
+      </c>
+      <c r="C63" s="32" t="s">
+        <v>74</v>
+      </c>
+      <c r="D63" s="36">
+        <v>45716</v>
+      </c>
+      <c r="E63" s="51">
+        <v>45730</v>
+      </c>
+      <c r="F63">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A64" s="50" t="s">
+        <v>92</v>
+      </c>
+      <c r="B64" s="32" t="s">
+        <v>71</v>
+      </c>
+      <c r="C64" s="32" t="s">
+        <v>75</v>
+      </c>
+      <c r="D64" s="36">
+        <v>45741</v>
+      </c>
+      <c r="E64" s="51">
+        <v>45755</v>
+      </c>
+      <c r="F64">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A65" s="50" t="s">
+        <v>92</v>
+      </c>
+      <c r="B65" s="32" t="s">
+        <v>71</v>
+      </c>
+      <c r="C65" s="32" t="s">
+        <v>76</v>
+      </c>
+      <c r="D65" s="36">
+        <v>45769</v>
+      </c>
+      <c r="E65" s="51">
+        <v>45783</v>
+      </c>
+      <c r="F65">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A66" s="50" t="s">
+        <v>92</v>
+      </c>
+      <c r="B66" s="32" t="s">
+        <v>71</v>
+      </c>
+      <c r="C66" s="32" t="s">
+        <v>87</v>
+      </c>
+      <c r="D66" s="33">
+        <v>45797</v>
+      </c>
+      <c r="E66" s="51">
+        <v>45811</v>
+      </c>
+      <c r="F66">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="52" t="s">
+        <v>92</v>
+      </c>
+      <c r="B67" s="28" t="s">
+        <v>71</v>
+      </c>
+      <c r="C67" s="28" t="s">
+        <v>87</v>
+      </c>
+      <c r="D67" s="34">
+        <v>45825</v>
+      </c>
+      <c r="E67" s="54">
+        <v>45838</v>
+      </c>
+      <c r="F67">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F67"/>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B67">
+      <formula1>INDIRECT(AD2)</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Frontera/Empleados.xlsx
+++ b/Frontera/Empleados.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\TarjetasQR\Frontera\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="A:\9_GES_ADMON_FINAN\Fabryzcio Ortiz\FRONTERA\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11715"/>
+    <workbookView xWindow="0" yWindow="240" windowWidth="23235" windowHeight="12675"/>
   </bookViews>
   <sheets>
     <sheet name="Empleados" sheetId="1" r:id="rId1"/>
@@ -21,24 +21,11 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Hoja2!$A$1:$F$67</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="857" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="957" uniqueCount="194">
   <si>
     <t>Id</t>
   </si>
@@ -507,6 +494,120 @@
   </si>
   <si>
     <t>(1)7136231113</t>
+  </si>
+  <si>
+    <t>CARLOS JOSE RODRIGUEZ RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>carlosrodriguez_r@hotmail.es</t>
+  </si>
+  <si>
+    <t>SAMUEL ALEJANDRO NARANJO LEGUIZAMON</t>
+  </si>
+  <si>
+    <t>ADM SUMINISTROS Y CONSULTORIA SAS</t>
+  </si>
+  <si>
+    <t>NICOLAS FELIPE VALENZUELA CASTRO</t>
+  </si>
+  <si>
+    <t>MAURICIO ALEJANDRO CALVO RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>ALEXANDRA VANESSA GAMBA CAMARGO</t>
+  </si>
+  <si>
+    <t>LGP CONSULTING S.A.S</t>
+  </si>
+  <si>
+    <t>DANIEL ALFONSO CELMA HIDALGO</t>
+  </si>
+  <si>
+    <t>FARLEY GARCIA OSORIO</t>
+  </si>
+  <si>
+    <t>OSWALDO JUNIOR SILVA MONROY</t>
+  </si>
+  <si>
+    <t>LADY JOHANA OROZCO ORTIZ</t>
+  </si>
+  <si>
+    <t>O-</t>
+  </si>
+  <si>
+    <t xml:space="preserve">samuel.alejo07@gmail.com </t>
+  </si>
+  <si>
+    <t>nf.nicolas@gmail.com</t>
+  </si>
+  <si>
+    <t>recalvo1976@gmail.com</t>
+  </si>
+  <si>
+    <t>alexandra.gamba@gmail.com</t>
+  </si>
+  <si>
+    <t>danielcelma@hotmail.com</t>
+  </si>
+  <si>
+    <t>farleygarciao@gmail.com</t>
+  </si>
+  <si>
+    <t>oilsilva@yahoo.com.ar</t>
+  </si>
+  <si>
+    <t>ladyjohannaorozcoortiz@outlook.com</t>
+  </si>
+  <si>
+    <t>901743818-4</t>
+  </si>
+  <si>
+    <t>901937902-9</t>
+  </si>
+  <si>
+    <t>CE 361804</t>
+  </si>
+  <si>
+    <t>ANDRES FELIPE RIOS RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>afrr96@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lfparragil@hotmail.com  </t>
+  </si>
+  <si>
+    <t>higuita1977@yahoo.es</t>
+  </si>
+  <si>
+    <t>MERIDIAN CO}NSULTING LTDA</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1qRzylXX-V5hN0xK1ROcOeHQxSzsbQ5jx/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1VYA146qkqp3fBexBL0HMFe5tB_HYXt9t/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1HMxV4lHAIyfeSRuFd2_tm2e2g9cK5wDC/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1TX0Ge6yg3kQhh50V2n14XRI1nf-xt5b8/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1DEIjp4mh8J3x-kAQwvxnGTNQGpYW0KrA/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1GCtnG5w0rBY2iDZ9bCsozDBi76MQaiEj/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1SqkHFxlK8rbKS6gx8YdG0f9zR5kaK5UQ/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/17l0svVoh3dtbezuMrmhPjZOHAONhJDa8/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1cWk1XU8JOCTexLEuG0INLZuYnS-z_8da/view?usp=sharing</t>
   </si>
 </sst>
 </file>
@@ -674,7 +775,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="38">
+  <fills count="40">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -884,8 +985,20 @@
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="40">
+  <borders count="46">
     <border>
       <left/>
       <right/>
@@ -1416,6 +1529,70 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1462,7 +1639,7 @@
     <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="123">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1540,9 +1717,6 @@
     <xf numFmtId="0" fontId="20" fillId="36" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="37" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1570,12 +1744,6 @@
     <xf numFmtId="14" fontId="19" fillId="37" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="37" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="20" fillId="37" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="37" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1633,12 +1801,6 @@
     <xf numFmtId="14" fontId="20" fillId="37" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="37" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="20" fillId="37" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="14" fontId="19" fillId="37" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1668,14 +1830,155 @@
     </xf>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="42" xfId="42" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="44" xfId="42" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="15" xfId="42" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="42" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="42" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" xfId="42" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="42" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="24" xfId="42" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="41" xfId="42" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="41" xfId="42" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="38" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="38" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="19" fillId="38" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="20" fillId="38" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="38" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="38" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="19" fillId="38" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="20" fillId="38" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="38" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="38" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="19" fillId="38" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="20" fillId="38" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="38" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="38" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="20" fillId="38" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="20" fillId="38" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="39" borderId="24" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="39" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="39" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Énfasis1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1776,8 +2079,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabla1" displayName="Tabla1" ref="A1:K21" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
-  <autoFilter ref="A1:K21"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabla1" displayName="Tabla1" ref="A1:K23" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
+  <autoFilter ref="A1:K23"/>
   <sortState ref="A5:K21">
     <sortCondition ref="B1:B21"/>
   </sortState>
@@ -2061,18 +2364,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K29"/>
+  <dimension ref="A1:K34"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.85546875" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="23.85546875" customWidth="1"/>
+    <col min="1" max="1" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40.140625" customWidth="1"/>
+    <col min="3" max="3" width="25.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.42578125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.140625" customWidth="1"/>
     <col min="6" max="6" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="26.7109375" customWidth="1"/>
+    <col min="7" max="7" width="31.42578125" customWidth="1"/>
     <col min="8" max="8" width="26.28515625" customWidth="1"/>
-    <col min="9" max="9" width="16.85546875" customWidth="1"/>
+    <col min="9" max="9" width="18.7109375" customWidth="1"/>
     <col min="10" max="10" width="21.85546875" customWidth="1"/>
     <col min="11" max="11" width="82.85546875" customWidth="1"/>
   </cols>
@@ -2087,10 +2390,10 @@
       <c r="C1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="71" t="s">
+      <c r="D1" s="65" t="s">
         <v>127</v>
       </c>
-      <c r="E1" s="71" t="s">
+      <c r="E1" s="65" t="s">
         <v>5</v>
       </c>
       <c r="F1" s="2" t="s">
@@ -2137,10 +2440,10 @@
       <c r="H2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="I2" s="72">
+      <c r="I2" s="66">
         <v>3138174050</v>
       </c>
-      <c r="J2" s="72" t="s">
+      <c r="J2" s="66" t="s">
         <v>155</v>
       </c>
       <c r="K2" s="3" t="s">
@@ -2172,10 +2475,10 @@
       <c r="H3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="I3" s="72">
+      <c r="I3" s="66">
         <v>3138174050</v>
       </c>
-      <c r="J3" s="72" t="s">
+      <c r="J3" s="66" t="s">
         <v>155</v>
       </c>
       <c r="K3" s="3" t="s">
@@ -2183,16 +2486,16 @@
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="2">
+      <c r="A4" s="84">
         <v>1121924878</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="86" t="s">
         <v>45</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="D4" s="1">
+      <c r="D4" s="88">
         <v>3124150309</v>
       </c>
       <c r="E4" s="1" t="s">
@@ -2204,48 +2507,48 @@
       <c r="G4" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="H4" s="76" t="s">
         <v>2</v>
       </c>
-      <c r="I4" s="72">
+      <c r="I4" s="66">
         <v>3138174050</v>
       </c>
-      <c r="J4" s="72" t="s">
+      <c r="J4" s="70" t="s">
         <v>155</v>
       </c>
-      <c r="K4" s="2" t="s">
-        <v>3</v>
+      <c r="K4" s="3" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="2">
+      <c r="A5" s="84">
         <v>1098774228</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="86" t="s">
         <v>28</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="D5" s="1">
+      <c r="D5" s="89">
         <v>3014187370</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="F5" s="88" t="s">
         <v>14</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="H5" s="27" t="s">
+      <c r="H5" s="76" t="s">
         <v>2</v>
       </c>
-      <c r="I5" s="72">
+      <c r="I5" s="66">
         <v>3138174050</v>
       </c>
-      <c r="J5" s="72" t="s">
+      <c r="J5" s="71" t="s">
         <v>155</v>
       </c>
       <c r="K5" s="3" t="s">
@@ -2253,34 +2556,34 @@
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" s="2">
+      <c r="A6" s="84">
         <v>74083945</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="86" t="s">
         <v>15</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="1">
+      <c r="D6" s="89">
         <v>3208495340</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="F6" s="89" t="s">
         <v>14</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H6" s="27" t="s">
+      <c r="H6" s="76" t="s">
         <v>2</v>
       </c>
-      <c r="I6" s="72">
+      <c r="I6" s="66">
         <v>3138174050</v>
       </c>
-      <c r="J6" s="72" t="s">
+      <c r="J6" s="71" t="s">
         <v>155</v>
       </c>
       <c r="K6" s="3" t="s">
@@ -2288,34 +2591,34 @@
       </c>
     </row>
     <row r="7" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="2">
+      <c r="A7" s="84">
         <v>1035854640</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="86" t="s">
         <v>34</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="D7" s="1">
+      <c r="D7" s="89">
         <v>3228990545</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="F7" s="89" t="s">
         <v>14</v>
       </c>
-      <c r="G7" s="3" t="s">
+      <c r="G7" s="92" t="s">
         <v>35</v>
       </c>
-      <c r="H7" s="1" t="s">
+      <c r="H7" s="76" t="s">
         <v>2</v>
       </c>
-      <c r="I7" s="72">
+      <c r="I7" s="66">
         <v>3138174050</v>
       </c>
-      <c r="J7" s="72" t="s">
+      <c r="J7" s="71" t="s">
         <v>155</v>
       </c>
       <c r="K7" s="2" t="s">
@@ -2323,34 +2626,34 @@
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" s="2">
+      <c r="A8" s="84">
         <v>80794172</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="86" t="s">
         <v>51</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D8" s="1">
+      <c r="D8" s="89">
         <v>3142421019</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="F8" s="89" t="s">
         <v>14</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="G8" s="92" t="s">
         <v>52</v>
       </c>
-      <c r="H8" s="27" t="s">
+      <c r="H8" s="76" t="s">
         <v>2</v>
       </c>
-      <c r="I8" s="72">
+      <c r="I8" s="66">
         <v>3138174050</v>
       </c>
-      <c r="J8" s="72" t="s">
+      <c r="J8" s="71" t="s">
         <v>155</v>
       </c>
       <c r="K8" s="3" t="s">
@@ -2358,34 +2661,34 @@
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A9" s="2">
+      <c r="A9" s="84">
         <v>1019133012</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="86" t="s">
         <v>36</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="D9" s="1">
+      <c r="D9" s="89">
         <v>3128894731</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="F9" s="89" t="s">
         <v>14</v>
       </c>
-      <c r="G9" s="3" t="s">
+      <c r="G9" s="92" t="s">
         <v>37</v>
       </c>
-      <c r="H9" s="27" t="s">
+      <c r="H9" s="76" t="s">
         <v>2</v>
       </c>
-      <c r="I9" s="72">
+      <c r="I9" s="66">
         <v>3138174050</v>
       </c>
-      <c r="J9" s="72" t="s">
+      <c r="J9" s="71" t="s">
         <v>155</v>
       </c>
       <c r="K9" s="3" t="s">
@@ -2393,34 +2696,34 @@
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10" s="2">
+      <c r="A10" s="84">
         <v>1019152161</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="86" t="s">
         <v>38</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="D10" s="1">
+      <c r="D10" s="89">
         <v>3178958725</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="F10" s="89" t="s">
         <v>14</v>
       </c>
-      <c r="G10" s="3" t="s">
+      <c r="G10" s="92" t="s">
         <v>39</v>
       </c>
-      <c r="H10" s="27" t="s">
+      <c r="H10" s="76" t="s">
         <v>2</v>
       </c>
-      <c r="I10" s="72">
+      <c r="I10" s="66">
         <v>3138174050</v>
       </c>
-      <c r="J10" s="72" t="s">
+      <c r="J10" s="71" t="s">
         <v>155</v>
       </c>
       <c r="K10" s="3" t="s">
@@ -2428,34 +2731,34 @@
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A11" s="2">
+      <c r="A11" s="84">
         <v>1082898312</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="86" t="s">
         <v>20</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="1">
+      <c r="D11" s="89">
         <v>3015001273</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F11" s="1" t="s">
+      <c r="F11" s="89" t="s">
         <v>14</v>
       </c>
-      <c r="G11" s="3" t="s">
+      <c r="G11" s="92" t="s">
         <v>21</v>
       </c>
-      <c r="H11" s="1" t="s">
+      <c r="H11" s="75" t="s">
         <v>2</v>
       </c>
-      <c r="I11" s="72">
+      <c r="I11" s="66">
         <v>3138174050</v>
       </c>
-      <c r="J11" s="72" t="s">
+      <c r="J11" s="71" t="s">
         <v>155</v>
       </c>
       <c r="K11" s="3" t="s">
@@ -2463,34 +2766,34 @@
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" s="2">
+      <c r="A12" s="84">
         <v>83168382</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="86" t="s">
         <v>55</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D12" s="1">
+      <c r="D12" s="89">
         <v>3152946638</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F12" s="1" t="s">
+      <c r="F12" s="89" t="s">
         <v>14</v>
       </c>
-      <c r="G12" s="3" t="s">
+      <c r="G12" s="92" t="s">
         <v>56</v>
       </c>
-      <c r="H12" s="1" t="s">
+      <c r="H12" s="75" t="s">
         <v>2</v>
       </c>
-      <c r="I12" s="72">
+      <c r="I12" s="66">
         <v>3138174050</v>
       </c>
-      <c r="J12" s="72" t="s">
+      <c r="J12" s="71" t="s">
         <v>155</v>
       </c>
       <c r="K12" s="3" t="s">
@@ -2498,34 +2801,34 @@
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="2">
+      <c r="A13" s="84">
         <v>1075213439</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="86" t="s">
         <v>49</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="D13" s="1">
+      <c r="D13" s="89">
         <v>3204432121</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F13" s="1" t="s">
+      <c r="F13" s="89" t="s">
         <v>14</v>
       </c>
-      <c r="G13" s="3" t="s">
+      <c r="G13" s="92" t="s">
         <v>50</v>
       </c>
-      <c r="H13" s="1" t="s">
+      <c r="H13" s="76" t="s">
         <v>2</v>
       </c>
-      <c r="I13" s="72">
+      <c r="I13" s="66">
         <v>3138174050</v>
       </c>
-      <c r="J13" s="72" t="s">
+      <c r="J13" s="71" t="s">
         <v>155</v>
       </c>
       <c r="K13" s="2" t="s">
@@ -2533,34 +2836,34 @@
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" s="2">
+      <c r="A14" s="84">
         <v>1233890099</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="86" t="s">
         <v>40</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="D14" s="1">
+      <c r="D14" s="89">
         <v>3057670925</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F14" s="1" t="s">
+      <c r="F14" s="89" t="s">
         <v>14</v>
       </c>
-      <c r="G14" s="3" t="s">
+      <c r="G14" s="92" t="s">
         <v>41</v>
       </c>
-      <c r="H14" s="1" t="s">
+      <c r="H14" s="76" t="s">
         <v>2</v>
       </c>
-      <c r="I14" s="72">
+      <c r="I14" s="66">
         <v>3138174050</v>
       </c>
-      <c r="J14" s="72" t="s">
+      <c r="J14" s="71" t="s">
         <v>155</v>
       </c>
       <c r="K14" s="2" t="s">
@@ -2568,34 +2871,34 @@
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15" s="2">
+      <c r="A15" s="84">
         <v>1018408231</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="86" t="s">
         <v>24</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D15" s="1">
+      <c r="D15" s="89">
         <v>3176963137</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F15" s="1" t="s">
+      <c r="F15" s="89" t="s">
         <v>14</v>
       </c>
-      <c r="G15" s="3" t="s">
+      <c r="G15" s="92" t="s">
         <v>25</v>
       </c>
-      <c r="H15" s="27" t="s">
+      <c r="H15" s="76" t="s">
         <v>2</v>
       </c>
-      <c r="I15" s="72">
+      <c r="I15" s="66">
         <v>3138174050</v>
       </c>
-      <c r="J15" s="72" t="s">
+      <c r="J15" s="71" t="s">
         <v>155</v>
       </c>
       <c r="K15" s="3" t="s">
@@ -2603,256 +2906,698 @@
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" s="2">
-        <v>1017222178</v>
-      </c>
-      <c r="B16" t="s">
-        <v>32</v>
+      <c r="A16" s="84">
+        <v>1054678905</v>
+      </c>
+      <c r="B16" s="122" t="s">
+        <v>156</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="D16" s="1">
-        <v>3202818282</v>
+        <v>12</v>
+      </c>
+      <c r="D16" s="89">
+        <v>3186425461</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F16" s="1" t="s">
+      <c r="F16" s="89" t="s">
         <v>14</v>
       </c>
-      <c r="G16" s="3" t="s">
+      <c r="G16" s="92" t="s">
+        <v>157</v>
+      </c>
+      <c r="H16" s="75" t="s">
+        <v>2</v>
+      </c>
+      <c r="I16" s="66">
+        <v>3138174050</v>
+      </c>
+      <c r="J16" s="71" t="s">
+        <v>155</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17" s="84">
+        <v>1017222178</v>
+      </c>
+      <c r="B17" s="86" t="s">
+        <v>32</v>
+      </c>
+      <c r="C17" s="81" t="s">
+        <v>132</v>
+      </c>
+      <c r="D17" s="89">
+        <v>3202818282</v>
+      </c>
+      <c r="E17" s="82" t="s">
+        <v>18</v>
+      </c>
+      <c r="F17" s="91" t="s">
+        <v>14</v>
+      </c>
+      <c r="G17" s="92" t="s">
         <v>33</v>
       </c>
-      <c r="H16" s="1" t="s">
+      <c r="H17" s="76" t="s">
         <v>2</v>
       </c>
-      <c r="I16" s="72">
+      <c r="I17" s="66">
         <v>3138174050</v>
       </c>
-      <c r="J16" s="72" t="s">
+      <c r="J17" s="71" t="s">
         <v>155</v>
       </c>
-      <c r="K16" s="2" t="s">
+      <c r="K17" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" s="2">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18" s="84">
+        <v>1075295138</v>
+      </c>
+      <c r="B18" s="86" t="s">
+        <v>180</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="D18" s="89">
+        <v>3186037019</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F18" s="91" t="s">
+        <v>14</v>
+      </c>
+      <c r="G18" s="92" t="s">
+        <v>181</v>
+      </c>
+      <c r="H18" s="76" t="s">
+        <v>2</v>
+      </c>
+      <c r="I18" s="66">
+        <v>3138174050</v>
+      </c>
+      <c r="J18" s="71" t="s">
+        <v>155</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A19" s="99">
         <v>1075276712</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B19" s="86" t="s">
         <v>42</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C19" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="D17" s="1">
+      <c r="D19" s="89">
         <v>3157939923</v>
       </c>
-      <c r="E17" s="1" t="s">
+      <c r="E19" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F17" s="1" t="s">
+      <c r="F19" s="89" t="s">
         <v>14</v>
       </c>
-      <c r="G17" s="3" t="s">
+      <c r="G19" s="92" t="s">
         <v>43</v>
       </c>
-      <c r="H17" s="1" t="s">
+      <c r="H19" s="76" t="s">
         <v>2</v>
       </c>
-      <c r="I17" s="72">
+      <c r="I19" s="66">
         <v>3138174050</v>
       </c>
-      <c r="J17" s="72" t="s">
+      <c r="J19" s="71" t="s">
         <v>155</v>
       </c>
-      <c r="K17" s="3"/>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" s="2">
+      <c r="K19" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A20" s="84">
         <v>1075250696</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B20" s="86" t="s">
         <v>22</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C20" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D18" s="1">
+      <c r="D20" s="89">
         <v>3187826413</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H18" s="27" t="s">
-        <v>2</v>
-      </c>
-      <c r="I18" s="72">
-        <v>3138174050</v>
-      </c>
-      <c r="J18" s="72" t="s">
-        <v>155</v>
-      </c>
-      <c r="K18" s="3" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A19" s="2">
-        <v>1098728440</v>
-      </c>
-      <c r="B19" t="s">
-        <v>53</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D19" s="1">
-        <v>3176801825</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="H19" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="I19" s="72">
-        <v>3138174050</v>
-      </c>
-      <c r="J19" s="72" t="s">
-        <v>155</v>
-      </c>
-      <c r="K19" s="3" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A20" s="2">
-        <v>1098712563</v>
-      </c>
-      <c r="B20" t="s">
-        <v>30</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="D20" s="1">
-        <v>3013715669</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F20" s="1" t="s">
+      <c r="F20" s="89" t="s">
         <v>14</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="H20" s="1" t="s">
+      <c r="G20" s="92" t="s">
+        <v>23</v>
+      </c>
+      <c r="H20" s="76" t="s">
         <v>2</v>
       </c>
-      <c r="I20" s="72">
+      <c r="I20" s="66">
         <v>3138174050</v>
       </c>
-      <c r="J20" s="72" t="s">
+      <c r="J20" s="71" t="s">
         <v>155</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A21" s="2">
-        <v>1075248439</v>
-      </c>
-      <c r="B21" t="s">
-        <v>141</v>
+      <c r="A21" s="84">
+        <v>1098728440</v>
+      </c>
+      <c r="B21" s="86" t="s">
+        <v>53</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D21" s="1">
+      <c r="D21" s="89">
+        <v>3176801825</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F21" s="89" t="s">
+        <v>14</v>
+      </c>
+      <c r="G21" s="92" t="s">
+        <v>54</v>
+      </c>
+      <c r="H21" s="75" t="s">
+        <v>2</v>
+      </c>
+      <c r="I21" s="66">
+        <v>3138174050</v>
+      </c>
+      <c r="J21" s="71" t="s">
+        <v>155</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A22" s="84">
+        <v>1098712563</v>
+      </c>
+      <c r="B22" s="86" t="s">
+        <v>30</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="D22" s="89">
+        <v>3013715669</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F22" s="89" t="s">
+        <v>14</v>
+      </c>
+      <c r="G22" s="92" t="s">
+        <v>31</v>
+      </c>
+      <c r="H22" s="75" t="s">
+        <v>2</v>
+      </c>
+      <c r="I22" s="66">
+        <v>3138174050</v>
+      </c>
+      <c r="J22" s="71" t="s">
+        <v>155</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A23" s="84">
+        <v>1075248439</v>
+      </c>
+      <c r="B23" s="86" t="s">
+        <v>141</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D23" s="89">
         <v>3107656528</v>
       </c>
-      <c r="E21" s="1" t="s">
+      <c r="E23" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F21" s="1" t="s">
+      <c r="F23" s="89" t="s">
         <v>14</v>
       </c>
-      <c r="G21" s="3" t="s">
+      <c r="G23" s="92" t="s">
         <v>17</v>
       </c>
-      <c r="H21" s="1" t="s">
+      <c r="H23" s="75" t="s">
         <v>2</v>
       </c>
-      <c r="I21" s="72">
+      <c r="I23" s="66">
         <v>3138174050</v>
       </c>
-      <c r="J21" s="72" t="s">
+      <c r="J23" s="71" t="s">
         <v>155</v>
       </c>
-      <c r="K21" s="3" t="s">
+      <c r="K23" s="3" t="s">
         <v>142</v>
       </c>
     </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A24" s="99">
+        <v>1013602713</v>
+      </c>
+      <c r="B24" s="121" t="s">
+        <v>158</v>
+      </c>
+      <c r="C24" s="98" t="s">
+        <v>12</v>
+      </c>
+      <c r="D24" s="90">
+        <v>3134768595</v>
+      </c>
+      <c r="E24" s="82" t="s">
+        <v>18</v>
+      </c>
+      <c r="F24" s="91" t="s">
+        <v>14</v>
+      </c>
+      <c r="G24" s="93" t="s">
+        <v>169</v>
+      </c>
+      <c r="H24" s="101" t="s">
+        <v>2</v>
+      </c>
+      <c r="I24" s="74">
+        <v>3138174050</v>
+      </c>
+      <c r="J24" s="73" t="s">
+        <v>155</v>
+      </c>
+      <c r="K24" s="69" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A25" s="68" t="s">
+        <v>177</v>
+      </c>
+      <c r="B25" s="87" t="s">
+        <v>159</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D25" s="71">
+        <v>3506989029</v>
+      </c>
+      <c r="E25" s="66" t="s">
+        <v>18</v>
+      </c>
+      <c r="F25" s="89" t="s">
+        <v>14</v>
+      </c>
+      <c r="G25" s="94" t="s">
+        <v>183</v>
+      </c>
+      <c r="H25" s="101" t="s">
+        <v>2</v>
+      </c>
+      <c r="I25" s="74">
+        <v>3138174050</v>
+      </c>
+      <c r="J25" s="72" t="s">
+        <v>155</v>
+      </c>
+      <c r="K25" s="67" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A26" s="68">
+        <v>80792740</v>
+      </c>
+      <c r="B26" s="87" t="s">
+        <v>160</v>
+      </c>
+      <c r="C26" s="85" t="s">
+        <v>12</v>
+      </c>
+      <c r="D26" s="73">
+        <v>3203020127</v>
+      </c>
+      <c r="E26" s="78" t="s">
+        <v>18</v>
+      </c>
+      <c r="F26" s="90" t="s">
+        <v>14</v>
+      </c>
+      <c r="G26" s="94" t="s">
+        <v>170</v>
+      </c>
+      <c r="H26" s="101" t="s">
+        <v>2</v>
+      </c>
+      <c r="I26" s="74">
+        <v>3138174050</v>
+      </c>
+      <c r="J26" s="72" t="s">
+        <v>155</v>
+      </c>
+      <c r="K26" s="67" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A27" s="68">
+        <v>79729680</v>
+      </c>
+      <c r="B27" s="120" t="s">
+        <v>161</v>
+      </c>
+      <c r="C27" s="81" t="s">
+        <v>12</v>
+      </c>
+      <c r="D27" s="72">
+        <v>3115215703</v>
+      </c>
+      <c r="E27" s="80" t="s">
+        <v>13</v>
+      </c>
+      <c r="F27" s="91" t="s">
+        <v>14</v>
+      </c>
+      <c r="G27" s="94" t="s">
+        <v>171</v>
+      </c>
+      <c r="H27" s="101" t="s">
+        <v>2</v>
+      </c>
+      <c r="I27" s="74">
+        <v>3138174050</v>
+      </c>
+      <c r="J27" s="72" t="s">
+        <v>155</v>
+      </c>
+      <c r="K27" s="100" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A28" s="68">
+        <v>1017129665</v>
+      </c>
+      <c r="B28" s="120" t="s">
+        <v>162</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D28" s="71">
+        <v>3173638011</v>
+      </c>
+      <c r="E28" s="66" t="s">
+        <v>18</v>
+      </c>
+      <c r="F28" s="89" t="s">
+        <v>14</v>
+      </c>
+      <c r="G28" s="94" t="s">
+        <v>172</v>
+      </c>
+      <c r="H28" s="101" t="s">
+        <v>2</v>
+      </c>
+      <c r="I28" s="74">
+        <v>3138174050</v>
+      </c>
+      <c r="J28" s="72" t="s">
+        <v>155</v>
+      </c>
+      <c r="K28" s="103" t="s">
+        <v>189</v>
+      </c>
+    </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="G29" s="70"/>
+      <c r="A29" s="68" t="s">
+        <v>178</v>
+      </c>
+      <c r="B29" s="120" t="s">
+        <v>163</v>
+      </c>
+      <c r="C29" s="85" t="s">
+        <v>12</v>
+      </c>
+      <c r="D29" s="73">
+        <v>3006080415</v>
+      </c>
+      <c r="E29" s="78" t="s">
+        <v>18</v>
+      </c>
+      <c r="F29" s="90" t="s">
+        <v>14</v>
+      </c>
+      <c r="G29" s="94" t="s">
+        <v>182</v>
+      </c>
+      <c r="H29" s="101" t="s">
+        <v>2</v>
+      </c>
+      <c r="I29" s="74">
+        <v>3138174050</v>
+      </c>
+      <c r="J29" s="72" t="s">
+        <v>155</v>
+      </c>
+      <c r="K29" s="100" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A30" s="79" t="s">
+        <v>179</v>
+      </c>
+      <c r="B30" s="120" t="s">
+        <v>164</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D30" s="71">
+        <v>3115529695</v>
+      </c>
+      <c r="E30" s="66" t="s">
+        <v>168</v>
+      </c>
+      <c r="F30" s="89" t="s">
+        <v>14</v>
+      </c>
+      <c r="G30" s="95" t="s">
+        <v>173</v>
+      </c>
+      <c r="H30" s="101" t="s">
+        <v>2</v>
+      </c>
+      <c r="I30" s="74">
+        <v>3138174050</v>
+      </c>
+      <c r="J30" s="72" t="s">
+        <v>155</v>
+      </c>
+      <c r="K30" s="100" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="79">
+        <v>75079902</v>
+      </c>
+      <c r="B31" s="121" t="s">
+        <v>165</v>
+      </c>
+      <c r="C31" s="85" t="s">
+        <v>12</v>
+      </c>
+      <c r="D31" s="73">
+        <v>3159067298</v>
+      </c>
+      <c r="E31" s="78" t="s">
+        <v>18</v>
+      </c>
+      <c r="F31" s="90" t="s">
+        <v>14</v>
+      </c>
+      <c r="G31" s="96" t="s">
+        <v>174</v>
+      </c>
+      <c r="H31" s="101" t="s">
+        <v>184</v>
+      </c>
+      <c r="I31" s="74">
+        <v>3138174050</v>
+      </c>
+      <c r="J31" s="72" t="s">
+        <v>155</v>
+      </c>
+      <c r="K31" s="94" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A32" s="79">
+        <v>79907285</v>
+      </c>
+      <c r="B32" s="83" t="s">
+        <v>166</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D32" s="71">
+        <v>3115612369</v>
+      </c>
+      <c r="E32" s="66" t="s">
+        <v>18</v>
+      </c>
+      <c r="F32" s="89" t="s">
+        <v>14</v>
+      </c>
+      <c r="G32" s="97" t="s">
+        <v>175</v>
+      </c>
+      <c r="H32" s="102" t="s">
+        <v>2</v>
+      </c>
+      <c r="I32" s="74">
+        <v>3138174050</v>
+      </c>
+      <c r="J32" s="73" t="s">
+        <v>155</v>
+      </c>
+      <c r="K32" s="67" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A33" s="79">
+        <v>53105775</v>
+      </c>
+      <c r="B33" s="121" t="s">
+        <v>167</v>
+      </c>
+      <c r="C33" s="85" t="s">
+        <v>12</v>
+      </c>
+      <c r="D33" s="73">
+        <v>3144915798</v>
+      </c>
+      <c r="E33" s="78" t="s">
+        <v>18</v>
+      </c>
+      <c r="F33" s="90" t="s">
+        <v>14</v>
+      </c>
+      <c r="G33" s="77" t="s">
+        <v>176</v>
+      </c>
+      <c r="H33" s="101" t="s">
+        <v>2</v>
+      </c>
+      <c r="I33" s="74">
+        <v>3138174050</v>
+      </c>
+      <c r="J33" s="72" t="s">
+        <v>155</v>
+      </c>
+      <c r="K33" s="100" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="E34" s="66"/>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="G6" r:id="rId1"/>
     <hyperlink ref="G11" r:id="rId2"/>
-    <hyperlink ref="G18" r:id="rId3"/>
+    <hyperlink ref="G20" r:id="rId3"/>
     <hyperlink ref="G15" r:id="rId4"/>
     <hyperlink ref="G2" r:id="rId5"/>
     <hyperlink ref="G5" r:id="rId6"/>
-    <hyperlink ref="G20" r:id="rId7"/>
-    <hyperlink ref="G16" r:id="rId8"/>
+    <hyperlink ref="G22" r:id="rId7"/>
+    <hyperlink ref="G17" r:id="rId8"/>
     <hyperlink ref="G7" r:id="rId9"/>
     <hyperlink ref="G10" r:id="rId10"/>
     <hyperlink ref="G14" r:id="rId11"/>
-    <hyperlink ref="G17" r:id="rId12"/>
+    <hyperlink ref="G19" r:id="rId12"/>
     <hyperlink ref="G4" r:id="rId13"/>
     <hyperlink ref="G3" r:id="rId14"/>
     <hyperlink ref="G13" r:id="rId15"/>
     <hyperlink ref="G8" r:id="rId16"/>
-    <hyperlink ref="G19" r:id="rId17"/>
+    <hyperlink ref="G21" r:id="rId17"/>
     <hyperlink ref="G12" r:id="rId18"/>
     <hyperlink ref="G9" r:id="rId19"/>
     <hyperlink ref="K5" r:id="rId20"/>
     <hyperlink ref="K10" r:id="rId21"/>
-    <hyperlink ref="K20" r:id="rId22"/>
-    <hyperlink ref="K18" r:id="rId23"/>
+    <hyperlink ref="K22" r:id="rId22"/>
+    <hyperlink ref="K20" r:id="rId23"/>
     <hyperlink ref="K6" r:id="rId24"/>
     <hyperlink ref="K9" r:id="rId25"/>
     <hyperlink ref="K15" r:id="rId26"/>
     <hyperlink ref="K8" r:id="rId27"/>
     <hyperlink ref="K12" r:id="rId28"/>
-    <hyperlink ref="K19" r:id="rId29"/>
+    <hyperlink ref="K21" r:id="rId29"/>
     <hyperlink ref="K3" r:id="rId30"/>
     <hyperlink ref="K2" r:id="rId31"/>
-    <hyperlink ref="K21" r:id="rId32"/>
-    <hyperlink ref="G21" r:id="rId33"/>
+    <hyperlink ref="K23" r:id="rId32"/>
+    <hyperlink ref="G23" r:id="rId33"/>
     <hyperlink ref="K11" r:id="rId34"/>
+    <hyperlink ref="G16" r:id="rId35"/>
+    <hyperlink ref="G25" r:id="rId36"/>
+    <hyperlink ref="G18" r:id="rId37"/>
+    <hyperlink ref="G27" r:id="rId38"/>
+    <hyperlink ref="G26" r:id="rId39"/>
+    <hyperlink ref="G28" r:id="rId40"/>
+    <hyperlink ref="G29" r:id="rId41"/>
+    <hyperlink ref="G30" r:id="rId42"/>
+    <hyperlink ref="G31" r:id="rId43"/>
+    <hyperlink ref="G32" r:id="rId44"/>
+    <hyperlink ref="G33" r:id="rId45"/>
+    <hyperlink ref="K16" r:id="rId46"/>
+    <hyperlink ref="K30" r:id="rId47"/>
+    <hyperlink ref="K4" r:id="rId48"/>
+    <hyperlink ref="K27" r:id="rId49"/>
+    <hyperlink ref="K28" r:id="rId50"/>
+    <hyperlink ref="K31" r:id="rId51"/>
+    <hyperlink ref="K33" r:id="rId52"/>
+    <hyperlink ref="K29" r:id="rId53"/>
+    <hyperlink ref="K24" r:id="rId54"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId35"/>
+    <tablePart r:id="rId55"/>
   </tableParts>
 </worksheet>
 </file>
@@ -4595,39 +5340,39 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="42" t="s">
+      <c r="A1" s="39" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="43" t="s">
+      <c r="B1" s="40" t="s">
         <v>58</v>
       </c>
-      <c r="C1" s="44" t="s">
+      <c r="C1" s="41" t="s">
         <v>60</v>
       </c>
-      <c r="D1" s="43" t="s">
+      <c r="D1" s="40" t="s">
         <v>143</v>
       </c>
-      <c r="E1" s="45" t="s">
+      <c r="E1" s="42" t="s">
         <v>144</v>
       </c>
-      <c r="F1" s="45" t="s">
+      <c r="F1" s="42" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="46" t="s">
+      <c r="A2" s="43" t="s">
         <v>83</v>
       </c>
-      <c r="B2" s="47" t="s">
+      <c r="B2" s="44" t="s">
         <v>70</v>
       </c>
-      <c r="C2" s="47" t="s">
+      <c r="C2" s="44" t="s">
         <v>64</v>
       </c>
-      <c r="D2" s="48">
+      <c r="D2" s="45">
         <v>45677</v>
       </c>
-      <c r="E2" s="49">
+      <c r="E2" s="46">
         <v>45692</v>
       </c>
       <c r="F2">
@@ -4635,19 +5380,19 @@
       </c>
     </row>
     <row r="3" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="50" t="s">
+      <c r="A3" s="47" t="s">
         <v>83</v>
       </c>
-      <c r="B3" s="32" t="s">
+      <c r="B3" s="31" t="s">
         <v>70</v>
       </c>
-      <c r="C3" s="32" t="s">
+      <c r="C3" s="31" t="s">
         <v>67</v>
       </c>
-      <c r="D3" s="33">
+      <c r="D3" s="32">
         <v>45702</v>
       </c>
-      <c r="E3" s="51">
+      <c r="E3" s="48">
         <v>45709</v>
       </c>
       <c r="F3">
@@ -4655,19 +5400,19 @@
       </c>
     </row>
     <row r="4" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="50" t="s">
+      <c r="A4" s="47" t="s">
         <v>83</v>
       </c>
-      <c r="B4" s="32" t="s">
+      <c r="B4" s="31" t="s">
         <v>70</v>
       </c>
-      <c r="C4" s="32" t="s">
+      <c r="C4" s="31" t="s">
         <v>74</v>
       </c>
-      <c r="D4" s="33">
+      <c r="D4" s="32">
         <v>45724</v>
       </c>
-      <c r="E4" s="51">
+      <c r="E4" s="48">
         <v>45736</v>
       </c>
       <c r="F4">
@@ -4675,19 +5420,19 @@
       </c>
     </row>
     <row r="5" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="50" t="s">
+      <c r="A5" s="47" t="s">
         <v>83</v>
       </c>
-      <c r="B5" s="32" t="s">
+      <c r="B5" s="31" t="s">
         <v>70</v>
       </c>
-      <c r="C5" s="32" t="s">
+      <c r="C5" s="31" t="s">
         <v>75</v>
       </c>
-      <c r="D5" s="33">
+      <c r="D5" s="32">
         <v>45752</v>
       </c>
-      <c r="E5" s="51">
+      <c r="E5" s="48">
         <v>45764</v>
       </c>
       <c r="F5">
@@ -4695,19 +5440,19 @@
       </c>
     </row>
     <row r="6" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="50" t="s">
+      <c r="A6" s="47" t="s">
         <v>83</v>
       </c>
-      <c r="B6" s="32" t="s">
+      <c r="B6" s="31" t="s">
         <v>65</v>
       </c>
-      <c r="C6" s="32" t="s">
+      <c r="C6" s="31" t="s">
         <v>76</v>
       </c>
-      <c r="D6" s="33">
+      <c r="D6" s="32">
         <v>45778</v>
       </c>
-      <c r="E6" s="51">
+      <c r="E6" s="48">
         <v>45790</v>
       </c>
       <c r="F6">
@@ -4715,19 +5460,19 @@
       </c>
     </row>
     <row r="7" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="50" t="s">
+      <c r="A7" s="47" t="s">
         <v>83</v>
       </c>
-      <c r="B7" s="32" t="s">
+      <c r="B7" s="31" t="s">
         <v>65</v>
       </c>
-      <c r="C7" s="32" t="s">
+      <c r="C7" s="31" t="s">
         <v>87</v>
       </c>
-      <c r="D7" s="36">
+      <c r="D7" s="35">
         <v>45805</v>
       </c>
-      <c r="E7" s="51">
+      <c r="E7" s="48">
         <v>45816</v>
       </c>
       <c r="F7">
@@ -4735,19 +5480,19 @@
       </c>
     </row>
     <row r="8" spans="1:6" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="52" t="s">
+      <c r="A8" s="49" t="s">
         <v>83</v>
       </c>
-      <c r="B8" s="28" t="s">
+      <c r="B8" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="C8" s="28" t="s">
+      <c r="C8" s="27" t="s">
         <v>88</v>
       </c>
-      <c r="D8" s="29">
+      <c r="D8" s="28">
         <v>45837</v>
       </c>
-      <c r="E8" s="53">
+      <c r="E8" s="50">
         <v>45850</v>
       </c>
       <c r="F8">
@@ -4755,19 +5500,19 @@
       </c>
     </row>
     <row r="9" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="46" t="s">
+      <c r="A9" s="43" t="s">
         <v>34</v>
       </c>
-      <c r="B9" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="C9" s="47" t="s">
+      <c r="B9" s="44" t="s">
+        <v>71</v>
+      </c>
+      <c r="C9" s="44" t="s">
         <v>67</v>
       </c>
-      <c r="D9" s="48">
+      <c r="D9" s="45">
         <v>45702</v>
       </c>
-      <c r="E9" s="49">
+      <c r="E9" s="46">
         <v>45716</v>
       </c>
       <c r="F9">
@@ -4775,19 +5520,19 @@
       </c>
     </row>
     <row r="10" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A10" s="50" t="s">
+      <c r="A10" s="47" t="s">
         <v>34</v>
       </c>
-      <c r="B10" s="32" t="s">
-        <v>71</v>
-      </c>
-      <c r="C10" s="32" t="s">
+      <c r="B10" s="31" t="s">
+        <v>71</v>
+      </c>
+      <c r="C10" s="31" t="s">
         <v>74</v>
       </c>
-      <c r="D10" s="36">
+      <c r="D10" s="35">
         <v>45730</v>
       </c>
-      <c r="E10" s="51">
+      <c r="E10" s="48">
         <v>45741</v>
       </c>
       <c r="F10">
@@ -4795,19 +5540,19 @@
       </c>
     </row>
     <row r="11" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A11" s="50" t="s">
+      <c r="A11" s="47" t="s">
         <v>34</v>
       </c>
-      <c r="B11" s="32" t="s">
-        <v>71</v>
-      </c>
-      <c r="C11" s="32" t="s">
+      <c r="B11" s="31" t="s">
+        <v>71</v>
+      </c>
+      <c r="C11" s="31" t="s">
         <v>75</v>
       </c>
-      <c r="D11" s="36">
+      <c r="D11" s="35">
         <v>45755</v>
       </c>
-      <c r="E11" s="51">
+      <c r="E11" s="48">
         <v>45769</v>
       </c>
       <c r="F11">
@@ -4815,19 +5560,19 @@
       </c>
     </row>
     <row r="12" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A12" s="50" t="s">
+      <c r="A12" s="47" t="s">
         <v>34</v>
       </c>
-      <c r="B12" s="32" t="s">
-        <v>71</v>
-      </c>
-      <c r="C12" s="32" t="s">
+      <c r="B12" s="31" t="s">
+        <v>71</v>
+      </c>
+      <c r="C12" s="31" t="s">
         <v>76</v>
       </c>
-      <c r="D12" s="36">
+      <c r="D12" s="35">
         <v>45783</v>
       </c>
-      <c r="E12" s="51">
+      <c r="E12" s="48">
         <v>45797</v>
       </c>
       <c r="F12">
@@ -4835,19 +5580,19 @@
       </c>
     </row>
     <row r="13" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A13" s="50" t="s">
+      <c r="A13" s="47" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="32" t="s">
-        <v>71</v>
-      </c>
-      <c r="C13" s="32" t="s">
+      <c r="B13" s="31" t="s">
+        <v>71</v>
+      </c>
+      <c r="C13" s="31" t="s">
         <v>87</v>
       </c>
-      <c r="D13" s="36">
+      <c r="D13" s="35">
         <v>45811</v>
       </c>
-      <c r="E13" s="51">
+      <c r="E13" s="48">
         <v>45825</v>
       </c>
       <c r="F13">
@@ -4855,19 +5600,19 @@
       </c>
     </row>
     <row r="14" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="50" t="s">
+      <c r="A14" s="47" t="s">
         <v>34</v>
       </c>
-      <c r="B14" s="32" t="s">
-        <v>71</v>
-      </c>
-      <c r="C14" s="32" t="s">
+      <c r="B14" s="31" t="s">
+        <v>71</v>
+      </c>
+      <c r="C14" s="31" t="s">
         <v>88</v>
       </c>
-      <c r="D14" s="33">
+      <c r="D14" s="32">
         <v>45853</v>
       </c>
-      <c r="E14" s="51">
+      <c r="E14" s="48">
         <v>45867</v>
       </c>
       <c r="F14">
@@ -4875,19 +5620,19 @@
       </c>
     </row>
     <row r="15" spans="1:6" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="52" t="s">
+      <c r="A15" s="49" t="s">
         <v>34</v>
       </c>
-      <c r="B15" s="28" t="s">
-        <v>71</v>
-      </c>
-      <c r="C15" s="28" t="s">
+      <c r="B15" s="27" t="s">
+        <v>71</v>
+      </c>
+      <c r="C15" s="27" t="s">
         <v>93</v>
       </c>
-      <c r="D15" s="34">
+      <c r="D15" s="33">
         <v>45881</v>
       </c>
-      <c r="E15" s="54">
+      <c r="E15" s="51">
         <v>45895</v>
       </c>
       <c r="F15">
@@ -4895,19 +5640,19 @@
       </c>
     </row>
     <row r="16" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A16" s="46" t="s">
+      <c r="A16" s="43" t="s">
         <v>97</v>
       </c>
-      <c r="B16" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="C16" s="47" t="s">
+      <c r="B16" s="44" t="s">
+        <v>71</v>
+      </c>
+      <c r="C16" s="44" t="s">
         <v>67</v>
       </c>
-      <c r="D16" s="55">
+      <c r="D16" s="52">
         <v>45695</v>
       </c>
-      <c r="E16" s="49">
+      <c r="E16" s="46">
         <v>45709</v>
       </c>
       <c r="F16">
@@ -4915,19 +5660,19 @@
       </c>
     </row>
     <row r="17" spans="1:6" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="52" t="s">
+      <c r="A17" s="49" t="s">
         <v>97</v>
       </c>
-      <c r="B17" s="28" t="s">
-        <v>71</v>
-      </c>
-      <c r="C17" s="28" t="s">
+      <c r="B17" s="27" t="s">
+        <v>71</v>
+      </c>
+      <c r="C17" s="27" t="s">
         <v>74</v>
       </c>
-      <c r="D17" s="34">
+      <c r="D17" s="33">
         <v>45723</v>
       </c>
-      <c r="E17" s="54">
+      <c r="E17" s="51">
         <v>45736</v>
       </c>
       <c r="F17">
@@ -4935,19 +5680,19 @@
       </c>
     </row>
     <row r="18" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A18" s="56" t="s">
+      <c r="A18" s="53" t="s">
         <v>97</v>
       </c>
-      <c r="B18" s="39" t="s">
-        <v>71</v>
-      </c>
-      <c r="C18" s="39" t="s">
+      <c r="B18" s="36" t="s">
+        <v>71</v>
+      </c>
+      <c r="C18" s="36" t="s">
         <v>76</v>
       </c>
-      <c r="D18" s="41">
+      <c r="D18" s="38">
         <v>45797</v>
       </c>
-      <c r="E18" s="57">
+      <c r="E18" s="54">
         <v>45811</v>
       </c>
       <c r="F18">
@@ -4955,19 +5700,19 @@
       </c>
     </row>
     <row r="19" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A19" s="50" t="s">
+      <c r="A19" s="47" t="s">
         <v>97</v>
       </c>
-      <c r="B19" s="32" t="s">
-        <v>71</v>
-      </c>
-      <c r="C19" s="32" t="s">
+      <c r="B19" s="31" t="s">
+        <v>71</v>
+      </c>
+      <c r="C19" s="31" t="s">
         <v>87</v>
       </c>
-      <c r="D19" s="33">
+      <c r="D19" s="32">
         <v>45825</v>
       </c>
-      <c r="E19" s="51">
+      <c r="E19" s="48">
         <v>45839</v>
       </c>
       <c r="F19">
@@ -4975,19 +5720,19 @@
       </c>
     </row>
     <row r="20" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A20" s="50" t="s">
+      <c r="A20" s="47" t="s">
         <v>97</v>
       </c>
-      <c r="B20" s="32" t="s">
-        <v>71</v>
-      </c>
-      <c r="C20" s="32" t="s">
+      <c r="B20" s="31" t="s">
+        <v>71</v>
+      </c>
+      <c r="C20" s="31" t="s">
         <v>88</v>
       </c>
-      <c r="D20" s="33">
+      <c r="D20" s="32">
         <v>45853</v>
       </c>
-      <c r="E20" s="51">
+      <c r="E20" s="48">
         <v>45867</v>
       </c>
       <c r="F20">
@@ -4995,19 +5740,19 @@
       </c>
     </row>
     <row r="21" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A21" s="50" t="s">
+      <c r="A21" s="47" t="s">
         <v>97</v>
       </c>
-      <c r="B21" s="32" t="s">
-        <v>71</v>
-      </c>
-      <c r="C21" s="32" t="s">
+      <c r="B21" s="31" t="s">
+        <v>71</v>
+      </c>
+      <c r="C21" s="31" t="s">
         <v>93</v>
       </c>
-      <c r="D21" s="33">
+      <c r="D21" s="32">
         <v>45881</v>
       </c>
-      <c r="E21" s="51">
+      <c r="E21" s="48">
         <v>45895</v>
       </c>
       <c r="F21">
@@ -5015,19 +5760,19 @@
       </c>
     </row>
     <row r="22" spans="1:6" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="52" t="s">
+      <c r="A22" s="49" t="s">
         <v>97</v>
       </c>
-      <c r="B22" s="28" t="s">
-        <v>71</v>
-      </c>
-      <c r="C22" s="28" t="s">
+      <c r="B22" s="27" t="s">
+        <v>71</v>
+      </c>
+      <c r="C22" s="27" t="s">
         <v>94</v>
       </c>
-      <c r="D22" s="34">
+      <c r="D22" s="33">
         <v>45909</v>
       </c>
-      <c r="E22" s="54">
+      <c r="E22" s="51">
         <v>45923</v>
       </c>
       <c r="F22">
@@ -5035,19 +5780,19 @@
       </c>
     </row>
     <row r="23" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A23" s="46" t="s">
+      <c r="A23" s="43" t="s">
         <v>40</v>
       </c>
-      <c r="B23" s="47" t="s">
+      <c r="B23" s="44" t="s">
         <v>73</v>
       </c>
-      <c r="C23" s="47" t="s">
+      <c r="C23" s="44" t="s">
         <v>64</v>
       </c>
-      <c r="D23" s="48">
+      <c r="D23" s="45">
         <v>45681</v>
       </c>
-      <c r="E23" s="49">
+      <c r="E23" s="46">
         <v>45695</v>
       </c>
       <c r="F23">
@@ -5055,19 +5800,19 @@
       </c>
     </row>
     <row r="24" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A24" s="50" t="s">
+      <c r="A24" s="47" t="s">
         <v>40</v>
       </c>
-      <c r="B24" s="32" t="s">
+      <c r="B24" s="31" t="s">
         <v>73</v>
       </c>
-      <c r="C24" s="32" t="s">
+      <c r="C24" s="31" t="s">
         <v>67</v>
       </c>
-      <c r="D24" s="33">
+      <c r="D24" s="32">
         <v>45709</v>
       </c>
-      <c r="E24" s="51">
+      <c r="E24" s="48">
         <v>45723</v>
       </c>
       <c r="F24">
@@ -5075,19 +5820,19 @@
       </c>
     </row>
     <row r="25" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A25" s="50" t="s">
+      <c r="A25" s="47" t="s">
         <v>40</v>
       </c>
-      <c r="B25" s="32" t="s">
+      <c r="B25" s="31" t="s">
         <v>73</v>
       </c>
-      <c r="C25" s="32" t="s">
+      <c r="C25" s="31" t="s">
         <v>74</v>
       </c>
-      <c r="D25" s="33">
+      <c r="D25" s="32">
         <v>45734</v>
       </c>
-      <c r="E25" s="51">
+      <c r="E25" s="48">
         <v>45743</v>
       </c>
       <c r="F25">
@@ -5095,19 +5840,19 @@
       </c>
     </row>
     <row r="26" spans="1:6" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="52" t="s">
+      <c r="A26" s="49" t="s">
         <v>40</v>
       </c>
-      <c r="B26" s="28" t="s">
+      <c r="B26" s="27" t="s">
         <v>73</v>
       </c>
-      <c r="C26" s="28" t="s">
+      <c r="C26" s="27" t="s">
         <v>145</v>
       </c>
-      <c r="D26" s="34">
+      <c r="D26" s="33">
         <v>45776</v>
       </c>
-      <c r="E26" s="54">
+      <c r="E26" s="51">
         <v>45790</v>
       </c>
       <c r="F26" t="s">
@@ -5115,19 +5860,19 @@
       </c>
     </row>
     <row r="27" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A27" s="56" t="s">
+      <c r="A27" s="104" t="s">
         <v>101</v>
       </c>
-      <c r="B27" s="39" t="s">
+      <c r="B27" s="105" t="s">
         <v>62</v>
       </c>
-      <c r="C27" s="39" t="s">
+      <c r="C27" s="105" t="s">
         <v>64</v>
       </c>
-      <c r="D27" s="40">
+      <c r="D27" s="106">
         <v>45688</v>
       </c>
-      <c r="E27" s="57">
+      <c r="E27" s="107">
         <v>45702</v>
       </c>
       <c r="F27">
@@ -5135,19 +5880,19 @@
       </c>
     </row>
     <row r="28" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A28" s="50" t="s">
+      <c r="A28" s="108" t="s">
         <v>101</v>
       </c>
-      <c r="B28" s="32" t="s">
+      <c r="B28" s="109" t="s">
         <v>62</v>
       </c>
-      <c r="C28" s="32" t="s">
+      <c r="C28" s="109" t="s">
         <v>67</v>
       </c>
-      <c r="D28" s="36">
+      <c r="D28" s="110">
         <v>45716</v>
       </c>
-      <c r="E28" s="51">
+      <c r="E28" s="111">
         <v>45727</v>
       </c>
       <c r="F28">
@@ -5155,19 +5900,19 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="52" t="s">
+      <c r="A29" s="112" t="s">
         <v>101</v>
       </c>
-      <c r="B29" s="28" t="s">
+      <c r="B29" s="113" t="s">
         <v>62</v>
       </c>
-      <c r="C29" s="28" t="s">
+      <c r="C29" s="113" t="s">
         <v>74</v>
       </c>
-      <c r="D29" s="29">
+      <c r="D29" s="114">
         <v>45734</v>
       </c>
-      <c r="E29" s="54">
+      <c r="E29" s="115">
         <v>45741</v>
       </c>
       <c r="F29">
@@ -5175,19 +5920,19 @@
       </c>
     </row>
     <row r="30" spans="1:6" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="58" t="s">
+      <c r="A30" s="116" t="s">
         <v>32</v>
       </c>
-      <c r="B30" s="37" t="s">
+      <c r="B30" s="117" t="s">
         <v>73</v>
       </c>
-      <c r="C30" s="37" t="s">
+      <c r="C30" s="117" t="s">
         <v>115</v>
       </c>
-      <c r="D30" s="38">
+      <c r="D30" s="118">
         <v>45709</v>
       </c>
-      <c r="E30" s="59">
+      <c r="E30" s="119">
         <v>45723</v>
       </c>
       <c r="F30" t="s">
@@ -5195,19 +5940,19 @@
       </c>
     </row>
     <row r="31" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A31" s="46" t="s">
+      <c r="A31" s="43" t="s">
         <v>11</v>
       </c>
-      <c r="B31" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="C31" s="47" t="s">
+      <c r="B31" s="44" t="s">
+        <v>71</v>
+      </c>
+      <c r="C31" s="44" t="s">
         <v>64</v>
       </c>
-      <c r="D31" s="48">
+      <c r="D31" s="45">
         <v>45667</v>
       </c>
-      <c r="E31" s="60">
+      <c r="E31" s="55">
         <v>45681</v>
       </c>
       <c r="F31">
@@ -5215,19 +5960,19 @@
       </c>
     </row>
     <row r="32" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A32" s="50" t="s">
+      <c r="A32" s="47" t="s">
         <v>11</v>
       </c>
-      <c r="B32" s="32" t="s">
-        <v>71</v>
-      </c>
-      <c r="C32" s="32" t="s">
+      <c r="B32" s="31" t="s">
+        <v>71</v>
+      </c>
+      <c r="C32" s="31" t="s">
         <v>67</v>
       </c>
-      <c r="D32" s="33">
+      <c r="D32" s="32">
         <v>45695</v>
       </c>
-      <c r="E32" s="51">
+      <c r="E32" s="48">
         <v>45709</v>
       </c>
       <c r="F32">
@@ -5235,19 +5980,19 @@
       </c>
     </row>
     <row r="33" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A33" s="50" t="s">
+      <c r="A33" s="47" t="s">
         <v>11</v>
       </c>
-      <c r="B33" s="32" t="s">
-        <v>71</v>
-      </c>
-      <c r="C33" s="32" t="s">
+      <c r="B33" s="31" t="s">
+        <v>71</v>
+      </c>
+      <c r="C33" s="31" t="s">
         <v>74</v>
       </c>
-      <c r="D33" s="33">
+      <c r="D33" s="32">
         <v>45723</v>
       </c>
-      <c r="E33" s="51">
+      <c r="E33" s="48">
         <v>45734</v>
       </c>
       <c r="F33">
@@ -5255,19 +6000,19 @@
       </c>
     </row>
     <row r="34" spans="1:6" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="52" t="s">
+      <c r="A34" s="49" t="s">
         <v>11</v>
       </c>
-      <c r="B34" s="28" t="s">
-        <v>71</v>
-      </c>
-      <c r="C34" s="28" t="s">
+      <c r="B34" s="27" t="s">
+        <v>71</v>
+      </c>
+      <c r="C34" s="27" t="s">
         <v>75</v>
       </c>
-      <c r="D34" s="35">
+      <c r="D34" s="34">
         <v>45743</v>
       </c>
-      <c r="E34" s="61">
+      <c r="E34" s="56">
         <v>45752</v>
       </c>
       <c r="F34">
@@ -5275,19 +6020,19 @@
       </c>
     </row>
     <row r="35" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A35" s="46" t="s">
+      <c r="A35" s="43" t="s">
         <v>85</v>
       </c>
-      <c r="B35" s="47" t="s">
+      <c r="B35" s="44" t="s">
         <v>70</v>
       </c>
-      <c r="C35" s="47" t="s">
+      <c r="C35" s="44" t="s">
         <v>67</v>
       </c>
-      <c r="D35" s="48">
+      <c r="D35" s="45">
         <v>45692</v>
       </c>
-      <c r="E35" s="49">
+      <c r="E35" s="46">
         <v>45702</v>
       </c>
       <c r="F35">
@@ -5295,19 +6040,19 @@
       </c>
     </row>
     <row r="36" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A36" s="50" t="s">
+      <c r="A36" s="47" t="s">
         <v>85</v>
       </c>
-      <c r="B36" s="32" t="s">
+      <c r="B36" s="31" t="s">
         <v>70</v>
       </c>
-      <c r="C36" s="32" t="s">
+      <c r="C36" s="31" t="s">
         <v>74</v>
       </c>
-      <c r="D36" s="33">
+      <c r="D36" s="32">
         <v>45709</v>
       </c>
-      <c r="E36" s="51">
+      <c r="E36" s="48">
         <v>45724</v>
       </c>
       <c r="F36">
@@ -5315,19 +6060,19 @@
       </c>
     </row>
     <row r="37" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A37" s="50" t="s">
+      <c r="A37" s="47" t="s">
         <v>85</v>
       </c>
-      <c r="B37" s="32" t="s">
+      <c r="B37" s="31" t="s">
         <v>70</v>
       </c>
-      <c r="C37" s="32" t="s">
+      <c r="C37" s="31" t="s">
         <v>75</v>
       </c>
-      <c r="D37" s="33">
+      <c r="D37" s="32">
         <v>45736</v>
       </c>
-      <c r="E37" s="51">
+      <c r="E37" s="48">
         <v>45753</v>
       </c>
       <c r="F37">
@@ -5335,19 +6080,19 @@
       </c>
     </row>
     <row r="38" spans="1:6" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="52" t="s">
+      <c r="A38" s="49" t="s">
         <v>85</v>
       </c>
-      <c r="B38" s="28" t="s">
+      <c r="B38" s="27" t="s">
         <v>70</v>
       </c>
-      <c r="C38" s="28" t="s">
+      <c r="C38" s="27" t="s">
         <v>76</v>
       </c>
-      <c r="D38" s="34">
+      <c r="D38" s="33">
         <v>45790</v>
       </c>
-      <c r="E38" s="54">
+      <c r="E38" s="51">
         <v>45804</v>
       </c>
       <c r="F38">
@@ -5355,19 +6100,19 @@
       </c>
     </row>
     <row r="39" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A39" s="46" t="s">
+      <c r="A39" s="43" t="s">
         <v>91</v>
       </c>
-      <c r="B39" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="C39" s="47" t="s">
+      <c r="B39" s="44" t="s">
+        <v>71</v>
+      </c>
+      <c r="C39" s="44" t="s">
         <v>64</v>
       </c>
-      <c r="D39" s="48">
+      <c r="D39" s="45">
         <v>45685</v>
       </c>
-      <c r="E39" s="49">
+      <c r="E39" s="46">
         <v>45702</v>
       </c>
       <c r="F39">
@@ -5375,19 +6120,19 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A40" s="50" t="s">
+      <c r="A40" s="47" t="s">
         <v>91</v>
       </c>
-      <c r="B40" s="32" t="s">
-        <v>71</v>
-      </c>
-      <c r="C40" s="32" t="s">
+      <c r="B40" s="31" t="s">
+        <v>71</v>
+      </c>
+      <c r="C40" s="31" t="s">
         <v>67</v>
       </c>
-      <c r="D40" s="36">
+      <c r="D40" s="35">
         <v>45716</v>
       </c>
-      <c r="E40" s="51">
+      <c r="E40" s="48">
         <v>45730</v>
       </c>
       <c r="F40">
@@ -5395,19 +6140,19 @@
       </c>
     </row>
     <row r="41" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A41" s="50" t="s">
+      <c r="A41" s="47" t="s">
         <v>91</v>
       </c>
-      <c r="B41" s="32" t="s">
-        <v>71</v>
-      </c>
-      <c r="C41" s="32" t="s">
+      <c r="B41" s="31" t="s">
+        <v>71</v>
+      </c>
+      <c r="C41" s="31" t="s">
         <v>74</v>
       </c>
-      <c r="D41" s="36">
+      <c r="D41" s="35">
         <v>45741</v>
       </c>
-      <c r="E41" s="51">
+      <c r="E41" s="48">
         <v>45755</v>
       </c>
       <c r="F41">
@@ -5415,19 +6160,19 @@
       </c>
     </row>
     <row r="42" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A42" s="50" t="s">
+      <c r="A42" s="47" t="s">
         <v>91</v>
       </c>
-      <c r="B42" s="32" t="s">
-        <v>71</v>
-      </c>
-      <c r="C42" s="32" t="s">
+      <c r="B42" s="31" t="s">
+        <v>71</v>
+      </c>
+      <c r="C42" s="31" t="s">
         <v>75</v>
       </c>
-      <c r="D42" s="33">
+      <c r="D42" s="32">
         <v>45769</v>
       </c>
-      <c r="E42" s="51">
+      <c r="E42" s="48">
         <v>45783</v>
       </c>
       <c r="F42">
@@ -5435,39 +6180,39 @@
       </c>
     </row>
     <row r="43" spans="1:6" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="62" t="s">
+      <c r="A43" s="57" t="s">
         <v>91</v>
       </c>
-      <c r="B43" s="30" t="s">
-        <v>71</v>
-      </c>
-      <c r="C43" s="30" t="s">
+      <c r="B43" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="C43" s="29" t="s">
         <v>146</v>
       </c>
-      <c r="D43" s="31">
+      <c r="D43" s="30">
         <v>45797</v>
       </c>
-      <c r="E43" s="63">
+      <c r="E43" s="58">
         <v>45811</v>
       </c>
-      <c r="F43" s="69" t="s">
+      <c r="F43" s="64" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A44" s="46" t="s">
+      <c r="A44" s="43" t="s">
         <v>99</v>
       </c>
-      <c r="B44" s="47" t="s">
+      <c r="B44" s="44" t="s">
         <v>62</v>
       </c>
-      <c r="C44" s="47" t="s">
+      <c r="C44" s="44" t="s">
         <v>64</v>
       </c>
-      <c r="D44" s="48">
+      <c r="D44" s="45">
         <v>45673</v>
       </c>
-      <c r="E44" s="49">
+      <c r="E44" s="46">
         <v>45688</v>
       </c>
       <c r="F44">
@@ -5475,19 +6220,19 @@
       </c>
     </row>
     <row r="45" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A45" s="50" t="s">
+      <c r="A45" s="47" t="s">
         <v>99</v>
       </c>
-      <c r="B45" s="32" t="s">
+      <c r="B45" s="31" t="s">
         <v>62</v>
       </c>
-      <c r="C45" s="32" t="s">
+      <c r="C45" s="31" t="s">
         <v>67</v>
       </c>
-      <c r="D45" s="36">
+      <c r="D45" s="35">
         <v>45702</v>
       </c>
-      <c r="E45" s="51">
+      <c r="E45" s="48">
         <v>45716</v>
       </c>
       <c r="F45">
@@ -5495,19 +6240,19 @@
       </c>
     </row>
     <row r="46" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A46" s="50" t="s">
+      <c r="A46" s="47" t="s">
         <v>99</v>
       </c>
-      <c r="B46" s="32" t="s">
+      <c r="B46" s="31" t="s">
         <v>62</v>
       </c>
-      <c r="C46" s="32" t="s">
+      <c r="C46" s="31" t="s">
         <v>74</v>
       </c>
-      <c r="D46" s="36">
+      <c r="D46" s="35">
         <v>45727</v>
       </c>
-      <c r="E46" s="51">
+      <c r="E46" s="48">
         <v>45734</v>
       </c>
       <c r="F46">
@@ -5515,19 +6260,19 @@
       </c>
     </row>
     <row r="47" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A47" s="50" t="s">
+      <c r="A47" s="47" t="s">
         <v>99</v>
       </c>
-      <c r="B47" s="32" t="s">
-        <v>71</v>
-      </c>
-      <c r="C47" s="32" t="s">
+      <c r="B47" s="31" t="s">
+        <v>71</v>
+      </c>
+      <c r="C47" s="31" t="s">
         <v>75</v>
       </c>
-      <c r="D47" s="33">
+      <c r="D47" s="32">
         <v>45783</v>
       </c>
-      <c r="E47" s="51">
+      <c r="E47" s="48">
         <v>45797</v>
       </c>
       <c r="F47">
@@ -5535,19 +6280,19 @@
       </c>
     </row>
     <row r="48" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A48" s="50" t="s">
+      <c r="A48" s="47" t="s">
         <v>99</v>
       </c>
-      <c r="B48" s="32" t="s">
-        <v>71</v>
-      </c>
-      <c r="C48" s="32" t="s">
+      <c r="B48" s="31" t="s">
+        <v>71</v>
+      </c>
+      <c r="C48" s="31" t="s">
         <v>76</v>
       </c>
-      <c r="D48" s="33">
+      <c r="D48" s="32">
         <v>45811</v>
       </c>
-      <c r="E48" s="51">
+      <c r="E48" s="48">
         <v>45825</v>
       </c>
       <c r="F48">
@@ -5555,19 +6300,19 @@
       </c>
     </row>
     <row r="49" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A49" s="50" t="s">
+      <c r="A49" s="47" t="s">
         <v>99</v>
       </c>
-      <c r="B49" s="32" t="s">
-        <v>71</v>
-      </c>
-      <c r="C49" s="32" t="s">
+      <c r="B49" s="31" t="s">
+        <v>71</v>
+      </c>
+      <c r="C49" s="31" t="s">
         <v>87</v>
       </c>
-      <c r="D49" s="33">
+      <c r="D49" s="32">
         <v>45839</v>
       </c>
-      <c r="E49" s="51">
+      <c r="E49" s="48">
         <v>45853</v>
       </c>
       <c r="F49">
@@ -5575,19 +6320,19 @@
       </c>
     </row>
     <row r="50" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A50" s="50" t="s">
+      <c r="A50" s="47" t="s">
         <v>99</v>
       </c>
-      <c r="B50" s="32" t="s">
-        <v>71</v>
-      </c>
-      <c r="C50" s="32" t="s">
+      <c r="B50" s="31" t="s">
+        <v>71</v>
+      </c>
+      <c r="C50" s="31" t="s">
         <v>88</v>
       </c>
-      <c r="D50" s="33">
+      <c r="D50" s="32">
         <v>45867</v>
       </c>
-      <c r="E50" s="51">
+      <c r="E50" s="48">
         <v>45881</v>
       </c>
       <c r="F50">
@@ -5595,19 +6340,19 @@
       </c>
     </row>
     <row r="51" spans="1:6" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="52" t="s">
+      <c r="A51" s="49" t="s">
         <v>99</v>
       </c>
-      <c r="B51" s="28" t="s">
-        <v>71</v>
-      </c>
-      <c r="C51" s="28" t="s">
+      <c r="B51" s="27" t="s">
+        <v>71</v>
+      </c>
+      <c r="C51" s="27" t="s">
         <v>120</v>
       </c>
-      <c r="D51" s="34">
+      <c r="D51" s="33">
         <v>45895</v>
       </c>
-      <c r="E51" s="54">
+      <c r="E51" s="51">
         <v>45909</v>
       </c>
       <c r="F51" t="s">
@@ -5615,19 +6360,19 @@
       </c>
     </row>
     <row r="52" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A52" s="56" t="s">
+      <c r="A52" s="53" t="s">
         <v>30</v>
       </c>
-      <c r="B52" s="39" t="s">
-        <v>71</v>
-      </c>
-      <c r="C52" s="39" t="s">
+      <c r="B52" s="36" t="s">
+        <v>71</v>
+      </c>
+      <c r="C52" s="36" t="s">
         <v>64</v>
       </c>
-      <c r="D52" s="40">
+      <c r="D52" s="37">
         <v>45674</v>
       </c>
-      <c r="E52" s="64">
+      <c r="E52" s="59">
         <v>45688</v>
       </c>
       <c r="F52">
@@ -5635,19 +6380,19 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A53" s="50" t="s">
+      <c r="A53" s="47" t="s">
         <v>30</v>
       </c>
-      <c r="B53" s="32" t="s">
-        <v>71</v>
-      </c>
-      <c r="C53" s="32" t="s">
+      <c r="B53" s="31" t="s">
+        <v>71</v>
+      </c>
+      <c r="C53" s="31" t="s">
         <v>67</v>
       </c>
-      <c r="D53" s="36">
+      <c r="D53" s="35">
         <v>45702</v>
       </c>
-      <c r="E53" s="51">
+      <c r="E53" s="48">
         <v>45716</v>
       </c>
       <c r="F53">
@@ -5655,19 +6400,19 @@
       </c>
     </row>
     <row r="54" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A54" s="50" t="s">
+      <c r="A54" s="47" t="s">
         <v>30</v>
       </c>
-      <c r="B54" s="32" t="s">
-        <v>71</v>
-      </c>
-      <c r="C54" s="32" t="s">
+      <c r="B54" s="31" t="s">
+        <v>71</v>
+      </c>
+      <c r="C54" s="31" t="s">
         <v>74</v>
       </c>
-      <c r="D54" s="36">
+      <c r="D54" s="35">
         <v>45730</v>
       </c>
-      <c r="E54" s="51">
+      <c r="E54" s="48">
         <v>45741</v>
       </c>
       <c r="F54">
@@ -5675,19 +6420,19 @@
       </c>
     </row>
     <row r="55" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A55" s="50" t="s">
+      <c r="A55" s="47" t="s">
         <v>30</v>
       </c>
-      <c r="B55" s="32" t="s">
-        <v>71</v>
-      </c>
-      <c r="C55" s="32" t="s">
+      <c r="B55" s="31" t="s">
+        <v>71</v>
+      </c>
+      <c r="C55" s="31" t="s">
         <v>75</v>
       </c>
-      <c r="D55" s="36">
+      <c r="D55" s="35">
         <v>45755</v>
       </c>
-      <c r="E55" s="51">
+      <c r="E55" s="48">
         <v>45769</v>
       </c>
       <c r="F55">
@@ -5695,19 +6440,19 @@
       </c>
     </row>
     <row r="56" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A56" s="50" t="s">
+      <c r="A56" s="47" t="s">
         <v>30</v>
       </c>
-      <c r="B56" s="32" t="s">
-        <v>71</v>
-      </c>
-      <c r="C56" s="32" t="s">
+      <c r="B56" s="31" t="s">
+        <v>71</v>
+      </c>
+      <c r="C56" s="31" t="s">
         <v>76</v>
       </c>
-      <c r="D56" s="33">
+      <c r="D56" s="32">
         <v>45783</v>
       </c>
-      <c r="E56" s="51">
+      <c r="E56" s="48">
         <v>45797</v>
       </c>
       <c r="F56">
@@ -5715,19 +6460,19 @@
       </c>
     </row>
     <row r="57" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A57" s="50" t="s">
+      <c r="A57" s="47" t="s">
         <v>30</v>
       </c>
-      <c r="B57" s="32" t="s">
-        <v>71</v>
-      </c>
-      <c r="C57" s="32" t="s">
+      <c r="B57" s="31" t="s">
+        <v>71</v>
+      </c>
+      <c r="C57" s="31" t="s">
         <v>87</v>
       </c>
-      <c r="D57" s="33">
+      <c r="D57" s="32">
         <v>45811</v>
       </c>
-      <c r="E57" s="51">
+      <c r="E57" s="48">
         <v>45825</v>
       </c>
       <c r="F57">
@@ -5735,19 +6480,19 @@
       </c>
     </row>
     <row r="58" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A58" s="50" t="s">
+      <c r="A58" s="47" t="s">
         <v>30</v>
       </c>
-      <c r="B58" s="32" t="s">
-        <v>71</v>
-      </c>
-      <c r="C58" s="32" t="s">
+      <c r="B58" s="31" t="s">
+        <v>71</v>
+      </c>
+      <c r="C58" s="31" t="s">
         <v>88</v>
       </c>
-      <c r="D58" s="33">
+      <c r="D58" s="32">
         <v>45839</v>
       </c>
-      <c r="E58" s="51">
+      <c r="E58" s="48">
         <v>45853</v>
       </c>
       <c r="F58">
@@ -5755,19 +6500,19 @@
       </c>
     </row>
     <row r="59" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A59" s="50" t="s">
+      <c r="A59" s="47" t="s">
         <v>30</v>
       </c>
-      <c r="B59" s="32" t="s">
-        <v>71</v>
-      </c>
-      <c r="C59" s="32" t="s">
+      <c r="B59" s="31" t="s">
+        <v>71</v>
+      </c>
+      <c r="C59" s="31" t="s">
         <v>93</v>
       </c>
-      <c r="D59" s="33">
+      <c r="D59" s="32">
         <v>45867</v>
       </c>
-      <c r="E59" s="51">
+      <c r="E59" s="48">
         <v>45881</v>
       </c>
       <c r="F59">
@@ -5775,19 +6520,19 @@
       </c>
     </row>
     <row r="60" spans="1:6" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="62" t="s">
+      <c r="A60" s="57" t="s">
         <v>30</v>
       </c>
-      <c r="B60" s="30" t="s">
-        <v>71</v>
-      </c>
-      <c r="C60" s="30" t="s">
+      <c r="B60" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="C60" s="29" t="s">
         <v>94</v>
       </c>
-      <c r="D60" s="31">
+      <c r="D60" s="30">
         <v>45895</v>
       </c>
-      <c r="E60" s="63">
+      <c r="E60" s="58">
         <v>45909</v>
       </c>
       <c r="F60">
@@ -5795,19 +6540,19 @@
       </c>
     </row>
     <row r="61" spans="1:6" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="65" t="s">
+      <c r="A61" s="60" t="s">
         <v>30</v>
       </c>
-      <c r="B61" s="66" t="s">
-        <v>71</v>
-      </c>
-      <c r="C61" s="66" t="s">
+      <c r="B61" s="61" t="s">
+        <v>71</v>
+      </c>
+      <c r="C61" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="D61" s="67">
+      <c r="D61" s="62">
         <v>46009</v>
       </c>
-      <c r="E61" s="68">
+      <c r="E61" s="63">
         <v>46022</v>
       </c>
       <c r="F61">
@@ -5815,19 +6560,19 @@
       </c>
     </row>
     <row r="62" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A62" s="46" t="s">
+      <c r="A62" s="43" t="s">
         <v>92</v>
       </c>
-      <c r="B62" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="C62" s="47" t="s">
+      <c r="B62" s="44" t="s">
+        <v>71</v>
+      </c>
+      <c r="C62" s="44" t="s">
         <v>147</v>
       </c>
-      <c r="D62" s="48">
+      <c r="D62" s="45">
         <v>45688</v>
       </c>
-      <c r="E62" s="49">
+      <c r="E62" s="46">
         <v>45702</v>
       </c>
       <c r="F62" t="s">
@@ -5835,19 +6580,19 @@
       </c>
     </row>
     <row r="63" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A63" s="50" t="s">
+      <c r="A63" s="47" t="s">
         <v>92</v>
       </c>
-      <c r="B63" s="32" t="s">
-        <v>71</v>
-      </c>
-      <c r="C63" s="32" t="s">
+      <c r="B63" s="31" t="s">
+        <v>71</v>
+      </c>
+      <c r="C63" s="31" t="s">
         <v>74</v>
       </c>
-      <c r="D63" s="36">
+      <c r="D63" s="35">
         <v>45716</v>
       </c>
-      <c r="E63" s="51">
+      <c r="E63" s="48">
         <v>45730</v>
       </c>
       <c r="F63">
@@ -5855,19 +6600,19 @@
       </c>
     </row>
     <row r="64" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A64" s="50" t="s">
+      <c r="A64" s="47" t="s">
         <v>92</v>
       </c>
-      <c r="B64" s="32" t="s">
-        <v>71</v>
-      </c>
-      <c r="C64" s="32" t="s">
+      <c r="B64" s="31" t="s">
+        <v>71</v>
+      </c>
+      <c r="C64" s="31" t="s">
         <v>75</v>
       </c>
-      <c r="D64" s="36">
+      <c r="D64" s="35">
         <v>45741</v>
       </c>
-      <c r="E64" s="51">
+      <c r="E64" s="48">
         <v>45755</v>
       </c>
       <c r="F64">
@@ -5875,19 +6620,19 @@
       </c>
     </row>
     <row r="65" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A65" s="50" t="s">
+      <c r="A65" s="47" t="s">
         <v>92</v>
       </c>
-      <c r="B65" s="32" t="s">
-        <v>71</v>
-      </c>
-      <c r="C65" s="32" t="s">
+      <c r="B65" s="31" t="s">
+        <v>71</v>
+      </c>
+      <c r="C65" s="31" t="s">
         <v>76</v>
       </c>
-      <c r="D65" s="36">
+      <c r="D65" s="35">
         <v>45769</v>
       </c>
-      <c r="E65" s="51">
+      <c r="E65" s="48">
         <v>45783</v>
       </c>
       <c r="F65">
@@ -5895,19 +6640,19 @@
       </c>
     </row>
     <row r="66" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A66" s="50" t="s">
+      <c r="A66" s="47" t="s">
         <v>92</v>
       </c>
-      <c r="B66" s="32" t="s">
-        <v>71</v>
-      </c>
-      <c r="C66" s="32" t="s">
+      <c r="B66" s="31" t="s">
+        <v>71</v>
+      </c>
+      <c r="C66" s="31" t="s">
         <v>87</v>
       </c>
-      <c r="D66" s="33">
+      <c r="D66" s="32">
         <v>45797</v>
       </c>
-      <c r="E66" s="51">
+      <c r="E66" s="48">
         <v>45811</v>
       </c>
       <c r="F66">
@@ -5915,19 +6660,19 @@
       </c>
     </row>
     <row r="67" spans="1:6" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="52" t="s">
+      <c r="A67" s="49" t="s">
         <v>92</v>
       </c>
-      <c r="B67" s="28" t="s">
-        <v>71</v>
-      </c>
-      <c r="C67" s="28" t="s">
+      <c r="B67" s="27" t="s">
+        <v>71</v>
+      </c>
+      <c r="C67" s="27" t="s">
         <v>87</v>
       </c>
-      <c r="D67" s="34">
+      <c r="D67" s="33">
         <v>45825</v>
       </c>
-      <c r="E67" s="54">
+      <c r="E67" s="51">
         <v>45838</v>
       </c>
       <c r="F67">
